--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.5675</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786076493</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>25.004405</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,110 +635,214 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>20.39624</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.375</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786082661</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>54.389973</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +643,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.5675</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786076493</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>25.004405</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,110 +747,214 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,47 +546,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20.39624</t>
+          <t>173</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786082661</t>
+          <t>1786086947</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>54.389973</t>
+          <t>503.272727</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>20.39624</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.375</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786082661</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>54.389973</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,28 +755,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.5675</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -779,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786076493</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>25.004405</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,110 +859,214 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>54.37</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.3588</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786086947</t>
+          <t>1786096483</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>503.272727</t>
+          <t>151.554007</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20.39624</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.3588</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786082661</t>
+          <t>1786095316</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>54.389973</t>
+          <t>15.69338</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>173</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -787,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786086947</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>503.272727</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,31 +867,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>20.39624</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.375</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -906,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786082661</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>54.389973</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,110 +979,318 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>14.19</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.5675</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1786076493</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>25.004405</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786096483</t>
+          <t>1786105696</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>151.554007</t>
+          <t>16.985121</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>4.49993</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.9463</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Over 0.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786095316</t>
+          <t>1786104752</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>15.69338</t>
+          <t>4.75554</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,22 +770,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>5.99989</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.945</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 0.5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786086947</t>
+          <t>1786104743</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>503.272727</t>
+          <t>6.34909</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,39 +867,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20.39624</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -907,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786082661</t>
+          <t>1786102413</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>54.389973</t>
+          <t>3.706122</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,28 +971,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.2212</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1026,7 +1018,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786102412</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>4.519774</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,23 +1075,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1115,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,17 +1152,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786102410</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>2.416918</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,110 +1179,870 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.195</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19403947</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1786102409</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1786207500</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>5.128205</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>54.37</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1786096483</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>151.554007</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1786095316</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>15.69338</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1786086947</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>503.272727</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20.39624</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.375</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1786082661</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>54.389973</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>14.19</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.5675</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1786076493</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>25.004405</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
+          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786105696</t>
+          <t>1786111515</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>16.985121</t>
+          <t>1.698514</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
+          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.49993</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.9463</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786104752</t>
+          <t>1786105696</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>4.75554</t>
+          <t>16.985121</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
+          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.99989</t>
+          <t>4.49993</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1.9463</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786104743</t>
+          <t>1786104752</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>6.34909</t>
+          <t>4.75554</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,31 +867,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.99989</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.945</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -899,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786102413</t>
+          <t>1786104743</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3.706122</t>
+          <t>6.34909</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -982,17 +990,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2212</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1018,7 +1026,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786102412</t>
+          <t>1786102413</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>4.519774</t>
+          <t>3.706122</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1091,12 +1099,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.2212</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1122,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786102410</t>
+          <t>1786102412</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2.416918</t>
+          <t>4.519774</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1195,12 +1203,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1211,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1256,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786102409</t>
+          <t>1786102410</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>5.128205</t>
+          <t>2.416918</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,39 +1291,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1323,27 +1323,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786096483</t>
+          <t>1786102409</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>151.554007</t>
+          <t>5.128205</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>54.37</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786095316</t>
+          <t>1786096483</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>15.69338</t>
+          <t>151.554007</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,12 +1507,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1522,22 +1522,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.3588</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786086947</t>
+          <t>1786095316</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>503.272727</t>
+          <t>15.69338</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1634,47 +1634,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20.39624</t>
+          <t>173</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786082661</t>
+          <t>1786086947</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>54.389973</t>
+          <t>503.272727</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,31 +1731,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>20.39624</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.375</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1763,27 +1771,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1808,17 +1816,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786082661</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>54.389973</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,28 +1843,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.5675</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1867,27 +1875,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1912,17 +1920,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786076493</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>25.004405</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,110 +1947,214 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
+          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.4563</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786111515</t>
+          <t>1786117951</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.698514</t>
+          <t>43.769863</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,39 +635,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
+          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.6812</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -683,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786105696</t>
+          <t>1786116835</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>16.985121</t>
+          <t>1.467861</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,39 +739,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
+          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.49993</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.9463</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Over 0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -795,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786104752</t>
+          <t>1786115830</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>4.75554</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,39 +843,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
+          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.99989</t>
+          <t>1.36999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Over 0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -907,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786104743</t>
+          <t>1786115829</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>6.34909</t>
+          <t>1.985493</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,28 +947,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1011,27 +979,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1024,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786102413</t>
+          <t>1786115827</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3.706122</t>
+          <t>1.463754</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,31 +1051,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2212</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1115,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786102412</t>
+          <t>1786115129</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>4.519774</t>
+          <t>13.559322</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,28 +1163,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.5075</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1219,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786102410</t>
+          <t>1786115128</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2.416918</t>
+          <t>9.852217</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,31 +1267,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1323,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1368,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786102409</t>
+          <t>1786115115</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>5.128205</t>
+          <t>85.387755</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,62 +1379,54 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>177.44126</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1480,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786096483</t>
+          <t>1786115115</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>151.554007</t>
+          <t>350.501254</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,12 +1483,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1522,12 +1498,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1537,7 +1513,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1547,27 +1523,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1592,17 +1568,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786095316</t>
+          <t>1786111515</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>15.69338</t>
+          <t>1.698514</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,12 +1595,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1634,22 +1610,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1659,27 +1635,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,17 +1680,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786086947</t>
+          <t>1786105696</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>503.272727</t>
+          <t>16.985121</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,12 +1707,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1746,22 +1722,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20.39624</t>
+          <t>4.49993</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.9463</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Over 0.5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1771,7 +1747,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1781,12 +1757,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1816,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786082661</t>
+          <t>1786104752</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1826,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>54.389973</t>
+          <t>4.75554</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,31 +1819,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>5.99989</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.945</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1875,27 +1859,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1920,17 +1904,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786104743</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>6.34909</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,28 +1931,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1979,27 +1963,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2024,17 +2008,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786102413</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>3.706122</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,110 +2035,1078 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.2212</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1786102412</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>4.519774</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1786102410</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2.416918</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.195</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19403947</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1786102409</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1786207500</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>5.128205</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>54.37</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1786096483</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>151.554007</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1786095316</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>15.69338</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1786086947</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>503.272727</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>20.39624</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.375</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1786082661</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>54.389973</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>14.19</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.5675</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1786076493</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>25.004405</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
+          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4563</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786117951</t>
+          <t>1786122007</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>43.769863</t>
+          <t>13.62862</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
+          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6812</t>
+          <t>1.4563</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -682,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786116835</t>
+          <t>1786117951</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.467861</t>
+          <t>43.769863</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +739,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
+          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.6812</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -771,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786115830</t>
+          <t>1786116835</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.467861</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
+          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.36999</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786115829</t>
+          <t>1786115830</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.985493</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
+          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -958,7 +958,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>1.36999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786115827</t>
+          <t>1786115829</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.463754</t>
+          <t>1.985493</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,27 +1051,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
+          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1079,11 +1075,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1091,27 +1083,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,17 +1128,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786115129</t>
+          <t>1786115827</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>13.559322</t>
+          <t>1.463754</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,7 +1155,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
+          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1171,7 +1163,11 @@
           <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1179,20 +1175,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786115128</t>
+          <t>1786115129</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>9.852217</t>
+          <t>13.559322</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,62 +1267,54 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
+          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5075</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1352,7 +1344,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786115128</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1354,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>85.387755</t>
+          <t>9.852217</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,7 +1371,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
+          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1387,28 +1379,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>177.44126</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>350.501254</t>
+          <t>85.387755</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,39 +1483,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
+          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>177.44126</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1523,27 +1515,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1568,17 +1560,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786111515</t>
+          <t>1786115115</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.698514</t>
+          <t>350.501254</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,12 +1587,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
+          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1610,7 +1602,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1680,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786105696</t>
+          <t>1786111515</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1682,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>16.985121</t>
+          <t>1.698514</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,7 +1699,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
+          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1722,22 +1714,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.49993</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.9463</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1747,27 +1739,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1792,17 +1784,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786104752</t>
+          <t>1786105696</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>4.75554</t>
+          <t>16.985121</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,7 +1811,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
+          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1834,12 +1826,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5.99989</t>
+          <t>4.49993</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1.9463</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1904,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786104743</t>
+          <t>1786104752</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1914,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>6.34909</t>
+          <t>4.75554</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1931,31 +1923,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.99989</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.945</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1963,27 +1963,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2008,17 +2008,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786102413</t>
+          <t>1786104743</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>3.706122</t>
+          <t>6.34909</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,7 +2035,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2046,17 +2046,17 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2212</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786102412</t>
+          <t>1786102413</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>4.519774</t>
+          <t>3.706122</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.2212</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786102410</t>
+          <t>1786102412</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.416918</t>
+          <t>4.519774</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2275,27 +2275,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2320,17 +2320,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786102409</t>
+          <t>1786102410</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>5.128205</t>
+          <t>2.416918</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2347,39 +2347,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2387,27 +2379,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2432,17 +2424,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786096483</t>
+          <t>1786102409</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>151.554007</t>
+          <t>5.128205</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,7 +2451,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2474,7 +2466,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>54.37</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2544,7 +2536,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786095316</t>
+          <t>1786096483</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2554,7 +2546,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>15.69338</t>
+          <t>151.554007</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,12 +2563,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2586,22 +2578,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.3588</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2626,7 +2618,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2656,7 +2648,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786086947</t>
+          <t>1786095316</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2666,7 +2658,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>503.272727</t>
+          <t>15.69338</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,12 +2675,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2698,47 +2690,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20.39624</t>
+          <t>173</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2768,7 +2760,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786082661</t>
+          <t>1786086947</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2778,7 +2770,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>54.389973</t>
+          <t>503.272727</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2795,31 +2787,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>20.39624</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.375</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2827,27 +2827,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786082661</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>54.389973</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,28 +2899,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.5675</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2931,27 +2931,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2976,17 +2976,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786076493</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>25.004405</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,110 +3003,214 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
+          <t>0x009e27d36e3bfb01593b611eb8138842f7baf97d375a4302c10337f4fa65da7a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786122007</t>
+          <t>1786128259</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13.62862</t>
+          <t>152.897196</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
+          <t>0x987370b50d0502b7fd566ef6bb2bf38112c25bf81110ad0b1926b02ffd8ccd9d</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4563</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -667,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786117951</t>
+          <t>1786127657</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>43.769863</t>
+          <t>5.94717</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
+          <t>0x38207556aceeaaa6ba9394fe5b398b808e1d67e0bba9c3b0fa61a88d5c5aebb7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>21.40562</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6812</t>
+          <t>1.0737</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -771,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786116835</t>
+          <t>1786126212</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.467861</t>
+          <t>290.245695</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,28 +867,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
+          <t>0x83a78ff6339d485633ea010240dad1c0ad7f4a30a2628cd7eb01ab0370275ddc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.76023</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -875,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786115830</t>
+          <t>1786125622</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.292389</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,28 +971,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
+          <t>0x5630ba52ae08208c16f996b3fc5f0ab29f63363f75b764a890d5196f1a24e9b9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x6e70489F443F69f1a091af8509f0b99338460D39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.36999</t>
+          <t>249.99999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -979,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,17 +1048,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786115829</t>
+          <t>1786125585</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.985493</t>
+          <t>469.483549</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,28 +1075,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
+          <t>0x272659eb9c2a40b218a61bdb98731190ae92104b09c8c08096e7cacce4e2dc79</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1083,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1128,17 +1152,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786115827</t>
+          <t>1786125525</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.463754</t>
+          <t>9.389671</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,62 +1179,54 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
+          <t>0xc8538d15c53a4c377da962db1d0193aab217862d8ad9ac90a3999b587e2a1c53</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>76.29599</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.5312</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1240,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786115129</t>
+          <t>1786125507</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>13.559322</t>
+          <t>143.615981</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,36 +1283,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
+          <t>0xcb1bccb079df818106a903bda81def1d78bea048113133314cb9b5de80505b9a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.14001</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -1314,7 +1338,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1344,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786115128</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1354,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>9.852217</t>
+          <t>10.894763</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,12 +1395,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
+          <t>0x7b5620344652130ca3f87e52b00289e9ee38aab6c426c0e9cd693b417361526c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1386,12 +1410,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1456,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>85.387755</t>
+          <t>157.894737</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,36 +1507,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
+          <t>0xdc6c27f0359af82e276a61c449bef19ee4c2778a601eecfac8b0ae278c4fed31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>177.44126</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.3787</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -1530,7 +1562,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1560,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786124228</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1570,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>350.501254</t>
+          <t>168.844884</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,12 +1619,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
+          <t>0xb740a9883984f2d057b5bd144c80df89d3be4972b6802619769be156582f7530</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1602,12 +1634,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>56.08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1617,7 +1649,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1627,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1672,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786111515</t>
+          <t>1786123222</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.698514</t>
+          <t>150.550336</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,12 +1731,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
+          <t>0x1eb675eb4dddff6e46c7fe87ea19a03c7d5274c16759609d8d9cad3c46312d55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1714,12 +1746,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1729,7 +1761,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1739,27 +1771,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1784,17 +1816,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786105696</t>
+          <t>1786123213</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>16.985121</t>
+          <t>14.349776</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,39 +1843,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
+          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.49993</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.9463</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Over 0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1851,7 +1875,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1861,12 +1885,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786104752</t>
+          <t>1786122007</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>4.75554</t>
+          <t>13.62862</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,39 +1947,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
+          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.99989</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1.4563</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Over 0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1963,7 +1979,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1973,12 +1989,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2008,7 +2024,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786104743</t>
+          <t>1786117951</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2018,7 +2034,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>6.34909</t>
+          <t>43.769863</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,28 +2051,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.6812</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2067,27 +2083,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2112,17 +2128,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786102413</t>
+          <t>1786116835</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3.706122</t>
+          <t>1.467861</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,28 +2155,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.2212</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2171,27 +2187,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2216,17 +2232,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786102412</t>
+          <t>1786115830</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>4.519774</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2243,28 +2259,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.36999</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2275,27 +2291,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2320,17 +2336,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786102410</t>
+          <t>1786115829</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2.416918</t>
+          <t>1.985493</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2347,28 +2363,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2379,27 +2395,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2424,17 +2440,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786102409</t>
+          <t>1786115827</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>5.128205</t>
+          <t>1.463754</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2451,12 +2467,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2466,12 +2482,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2536,7 +2552,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786096483</t>
+          <t>1786115129</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2546,7 +2562,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>151.554007</t>
+          <t>13.559322</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2563,62 +2579,54 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.5075</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2648,7 +2656,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786095316</t>
+          <t>1786115128</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2658,7 +2666,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>15.69338</t>
+          <t>9.852217</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2675,12 +2683,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2690,22 +2698,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2730,7 +2738,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2760,7 +2768,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786086947</t>
+          <t>1786115115</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2770,7 +2778,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>503.272727</t>
+          <t>85.387755</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,62 +2795,54 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20.39624</t>
+          <t>177.44126</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786082661</t>
+          <t>1786115115</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>54.389973</t>
+          <t>350.501254</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,31 +2899,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2931,27 +2939,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2976,17 +2984,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786111515</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>1.698514</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,31 +3011,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3035,27 +3051,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3080,17 +3096,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786105696</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>16.985121</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,110 +3123,1406 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4.49993</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.9463</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1786104752</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>4.75554</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5.99989</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.945</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1786104743</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>6.34909</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.6125</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1786102413</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>3.706122</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.2212</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1786102412</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>4.519774</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1786102410</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2.416918</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.195</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19403947</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1786102409</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1786207500</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>5.128205</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>54.37</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1786096483</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>151.554007</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1786095316</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>15.69338</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1786086947</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>503.272727</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>20.39624</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.375</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1786082661</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>54.389973</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>14.19</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.5675</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1786076493</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>25.004405</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V38"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x009e27d36e3bfb01593b611eb8138842f7baf97d375a4302c10337f4fa65da7a</t>
+          <t>0xd3c8bb8d02330d8124e995d21959103edcd0baaa6289b159970a2225912e418d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,31 +539,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786128259</t>
+          <t>1786135338</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>152.897196</t>
+          <t>4.792453</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x987370b50d0502b7fd566ef6bb2bf38112c25bf81110ad0b1926b02ffd8ccd9d</t>
+          <t>0xbdbdd9823b5c0238c109c0b23805ef0ff9a61aa34409f875e76398a0a7d6a460</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,31 +643,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>48.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -698,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786127657</t>
+          <t>1786135338</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>5.94717</t>
+          <t>181.283019</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x38207556aceeaaa6ba9394fe5b398b808e1d67e0bba9c3b0fa61a88d5c5aebb7</t>
+          <t>0x6e5e8a0fc2f92f97555f424e1454c8c7768aee012cd36da5c6482cae7684c76a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,47 +754,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21.40562</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.0737</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Fortuna Sittard</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Fortuna Sittard</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786126212</t>
+          <t>1786135337</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>290.245695</t>
+          <t>7.577358</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x83a78ff6339d485633ea010240dad1c0ad7f4a30a2628cd7eb01ab0370275ddc</t>
+          <t>0xe9b4cf790ad6491c958a9df98bf381066cbab97000c72aaa03df184df175418c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -875,23 +859,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.76023</t>
+          <t>8.36113</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -899,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786125622</t>
+          <t>1786135296</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>10.292389</t>
+          <t>25.241147</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,59 +963,67 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x5630ba52ae08208c16f996b3fc5f0ab29f63363f75b764a890d5196f1a24e9b9</t>
+          <t>0xadbd273938f30f3bb961943289c77aa5d38f5773b41a5f47fdaa69aaae6f92c6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x6e70489F443F69f1a091af8509f0b99338460D39</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>249.99999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.6513</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0x8a99a50823ade222f81f1405d35b66126a5baec6c8557587d907d6fc42ee8959</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1048,17 +1048,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786125585</t>
+          <t>1786133357</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>469.483549</t>
+          <t>7.677543</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,59 +1075,67 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x272659eb9c2a40b218a61bdb98731190ae92104b09c8c08096e7cacce4e2dc79</t>
+          <t>0x1fcc69e05756a9495c54cf92ec95cc3fa98841963ff82dbc95bde1118d0e88d6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13.75169</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786125525</t>
+          <t>1786132692</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>9.389671</t>
+          <t>41.514536</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,28 +1187,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xc8538d15c53a4c377da962db1d0193aab217862d8ad9ac90a3999b587e2a1c53</t>
+          <t>0x633e302e1f4a45e6cae190310048fc5640fdefddf9379c3100fb1c66a99ed226</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>76.29599</t>
+          <t>855.42</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5312</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1226,7 +1234,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1256,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786125507</t>
+          <t>1786129763</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>143.615981</t>
+          <t>1555.309091</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,7 +1291,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xcb1bccb079df818106a903bda81def1d78bea048113133314cb9b5de80505b9a</t>
+          <t>0x0630cb5bb6cb2cff5cff3d307163d367059153070ce4cc710f35aa8d5c0c6825</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1291,54 +1299,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.14001</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786124259</t>
+          <t>1786129750</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>10.894763</t>
+          <t>132.545455</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x7b5620344652130ca3f87e52b00289e9ee38aab6c426c0e9cd693b417361526c</t>
+          <t>0x7935024ab7987fd550aa17e789e9bdc95e2fbd51b52763713f00cf3fdfce8bdd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1403,54 +1403,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1480,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786124259</t>
+          <t>1786129738</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>157.894737</t>
+          <t>26.054545</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,7 +1499,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xdc6c27f0359af82e276a61c449bef19ee4c2778a601eecfac8b0ae278c4fed31</t>
+          <t>0x2b5a8f7ff44e3e83441016e9d07c7203d32fcbd029be82f693028e41ea14167e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1515,54 +1507,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>6.20999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3787</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1592,7 +1576,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786124228</t>
+          <t>1786129725</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1586,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>168.844884</t>
+          <t>11.290891</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,7 +1603,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xb740a9883984f2d057b5bd144c80df89d3be4972b6802619769be156582f7530</t>
+          <t>0x9be5cfaca91d026b377dc51c41481c7420f402caa117cd1a71bf175f81b8ba3f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1627,54 +1611,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>56.08</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3725</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1680,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786123222</t>
+          <t>1786129713</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1690,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>150.550336</t>
+          <t>31.436364</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,39 +1707,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x1eb675eb4dddff6e46c7fe87ea19a03c7d5274c16759609d8d9cad3c46312d55</t>
+          <t>0xffdb31c98c0c9e42bd2a3a4ac8c08c4dddf1bac9229455355ddf0f61eda11f5f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>52.93</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1786,7 +1754,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1816,7 +1784,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786123213</t>
+          <t>1786129699</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1826,7 +1794,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>14.349776</t>
+          <t>96.236364</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,28 +1811,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
+          <t>0x171c10e2c280f22ecd4a761a066bbcf7603ce72eb3464dbacf9b961ad202fb59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>215.36</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1890,7 +1858,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1920,7 +1888,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786122007</t>
+          <t>1786129686</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1930,7 +1898,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>13.62862</t>
+          <t>391.563636</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,31 +1915,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
+          <t>0x5ea684350a1a0b65d0f38be341db1516c1df4fe66d544944688193d0c3e3f0de</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>495.02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4563</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1994,7 +1970,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2024,7 +2000,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786117951</t>
+          <t>1786129356</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2034,7 +2010,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>43.769863</t>
+          <t>995.015075</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,31 +2027,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
+          <t>0x1a61ba580443c208fcf8a35afa56d0df4aaad017c49874a664c65a6551ec7d84</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>495.02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.6812</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2098,7 +2082,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2128,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786116835</t>
+          <t>1786129323</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2138,7 +2122,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.467861</t>
+          <t>995.015075</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,31 +2139,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
+          <t>0xbc4a52ef8f6d90db800339bd0fdc45e1e4887cc29721741fa364564427cebc93</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2187,27 +2179,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2232,17 +2224,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786115830</t>
+          <t>1786129297</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>97.507538</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,31 +2251,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
+          <t>0x009e27d36e3bfb01593b611eb8138842f7baf97d375a4302c10337f4fa65da7a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.36999</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2291,27 +2291,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786115829</t>
+          <t>1786128259</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.985493</t>
+          <t>152.897196</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,31 +2363,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
+          <t>0x987370b50d0502b7fd566ef6bb2bf38112c25bf81110ad0b1926b02ffd8ccd9d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2395,27 +2403,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2440,17 +2448,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786115827</t>
+          <t>1786127657</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.463754</t>
+          <t>5.94717</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,12 +2475,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
+          <t>0x38207556aceeaaa6ba9394fe5b398b808e1d67e0bba9c3b0fa61a88d5c5aebb7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2482,12 +2490,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21.40562</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.0737</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2497,7 +2505,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2507,27 +2515,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2552,17 +2560,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786115129</t>
+          <t>1786126212</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>13.559322</t>
+          <t>290.245695</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,28 +2587,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
+          <t>0x83a78ff6339d485633ea010240dad1c0ad7f4a30a2628cd7eb01ab0370275ddc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.76023</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2626,7 +2634,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2656,7 +2664,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786115128</t>
+          <t>1786125622</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2666,7 +2674,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>9.852217</t>
+          <t>10.292389</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,62 +2691,54 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
+          <t>0x5630ba52ae08208c16f996b3fc5f0ab29f63363f75b764a890d5196f1a24e9b9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x6e70489F443F69f1a091af8509f0b99338460D39</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>249.99999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786125585</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>85.387755</t>
+          <t>469.483549</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2795,23 +2795,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
+          <t>0x272659eb9c2a40b218a61bdb98731190ae92104b09c8c08096e7cacce4e2dc79</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>177.44126</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786125525</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>350.501254</t>
+          <t>9.389671</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,39 +2899,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
+          <t>0xc8538d15c53a4c377da962db1d0193aab217862d8ad9ac90a3999b587e2a1c53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76.29599</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.5312</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2939,27 +2931,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2984,17 +2976,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786111515</t>
+          <t>1786125507</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.698514</t>
+          <t>143.615981</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3011,12 +3003,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
+          <t>0xcb1bccb079df818106a903bda81def1d78bea048113133314cb9b5de80505b9a</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3026,12 +3018,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>4.14001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3041,7 +3033,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3051,27 +3043,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3096,17 +3088,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786105696</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>16.985121</t>
+          <t>10.894763</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3123,12 +3115,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
+          <t>0x7b5620344652130ca3f87e52b00289e9ee38aab6c426c0e9cd693b417361526c</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3138,22 +3130,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.49993</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.9463</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3163,7 +3155,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3173,12 +3165,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3208,7 +3200,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786104752</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3218,7 +3210,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>4.75554</t>
+          <t>157.894737</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3235,12 +3227,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
+          <t>0xdc6c27f0359af82e276a61c449bef19ee4c2778a601eecfac8b0ae278c4fed31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3250,22 +3242,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5.99989</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1.3787</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3275,7 +3267,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3285,12 +3277,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3320,7 +3312,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786104743</t>
+          <t>1786124228</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3330,7 +3322,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>6.34909</t>
+          <t>168.844884</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3347,31 +3339,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+          <t>0xb740a9883984f2d057b5bd144c80df89d3be4972b6802619769be156582f7530</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>56.08</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3379,27 +3379,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3424,17 +3424,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786102413</t>
+          <t>1786123222</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>3.706122</t>
+          <t>150.550336</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3451,31 +3451,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+          <t>0x1eb675eb4dddff6e46c7fe87ea19a03c7d5274c16759609d8d9cad3c46312d55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.2212</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3483,27 +3491,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3528,17 +3536,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786102412</t>
+          <t>1786123213</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>4.519774</t>
+          <t>14.349776</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3555,28 +3563,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3587,27 +3595,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3632,17 +3640,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786102410</t>
+          <t>1786122007</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2.416918</t>
+          <t>13.62862</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3659,28 +3667,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.4563</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3691,27 +3699,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3736,17 +3744,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786102409</t>
+          <t>1786117951</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>5.128205</t>
+          <t>43.769863</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3763,62 +3771,54 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.6812</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786096483</t>
+          <t>1786116835</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>151.554007</t>
+          <t>1.467861</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3875,27 +3875,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3903,11 +3899,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3915,27 +3907,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3960,17 +3952,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786095316</t>
+          <t>1786115830</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>15.69338</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3987,39 +3979,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>1.36999</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4027,27 +4011,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4072,17 +4056,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786086947</t>
+          <t>1786115829</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>503.272727</t>
+          <t>1.985493</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4099,27 +4083,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20.39624</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4127,11 +4107,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4139,27 +4115,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4184,17 +4160,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786082661</t>
+          <t>1786115827</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>54.389973</t>
+          <t>1.463754</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4211,31 +4187,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4243,27 +4227,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4288,17 +4272,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786115129</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>13.559322</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4315,28 +4299,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.5075</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4362,7 +4346,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4392,7 +4376,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786115128</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4402,7 +4386,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>9.852217</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,110 +4403,1846 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>31.38</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.3675</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1786115115</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>85.387755</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>177.44126</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.5063</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1786115115</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>350.501254</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.5888</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19403947</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1786111515</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1786207500</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1.698514</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>9.99999</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.5888</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19403947</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1786105696</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1786207500</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>16.985121</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4.49993</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.9463</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1786104752</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>4.75554</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5.99989</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.945</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1786104743</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>6.34909</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.6125</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1786102413</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>3.706122</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.2212</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1786102412</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>4.519774</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1786102410</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2.416918</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.195</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19403947</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1786102409</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1786207500</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>5.128205</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>54.37</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1786096483</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>151.554007</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1786095316</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>15.69338</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1786086947</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>503.272727</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>20.39624</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.375</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1786082661</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>54.389973</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>14.19</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.5675</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1786076493</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>25.004405</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd3c8bb8d02330d8124e995d21959103edcd0baaa6289b159970a2225912e418d</t>
+          <t>0x7eaedb8f4752259366867abf771d84c0d99e47010227fd51681abeb60b48411b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.1638</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
+          <t>0xc998a4ccb6265ea2336288383810c1b769d49949dbefbe46fcd473372116b82c</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786135338</t>
+          <t>1786146812</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4.792453</t>
+          <t>6.10687</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xbdbdd9823b5c0238c109c0b23805ef0ff9a61aa34409f875e76398a0a7d6a460</t>
+          <t>0xc17004473d1c14453448f29404ac7988d663c0f1eac3d80503d006f04db8d7a6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
+          <t>0x836ea569e8bb4a65752149e8c476f1184a85ddb5570c5106624ba137f9a0a2d5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786135338</t>
+          <t>1786146806</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>181.283019</t>
+          <t>2.684564</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,39 +739,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x6e5e8a0fc2f92f97555f424e1454c8c7768aee012cd36da5c6482cae7684c76a</t>
+          <t>0x88de27964fdb5afcbdf9d01c80c57e6ae6197056927b86aeb5d5e9260acc2828</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.0775</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -779,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xca6f32a50927cbde2cb395d95e723ecf21a4b1811b744369dad7d460f821dd6d</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786135337</t>
+          <t>1786146805</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>7.577358</t>
+          <t>12.903226</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,39 +843,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xe9b4cf790ad6491c958a9df98bf381066cbab97000c72aaa03df184df175418c</t>
+          <t>0x7c22fadfd0e1f902b93e750db5984c247214d30b4fe99214ef93a9e2ad497877</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.36113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.1625</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -891,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>PEC Zwolle vs Ajax Amsterdam</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Ajax Amsterdam</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xdd44346ee5e92ddeb574c7b372f2f6e8cfcd74de2a5309e9003a1550bcc12ab0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403941</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786135296</t>
+          <t>1786146805</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>25.241147</t>
+          <t>6.153846</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,12 +947,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xadbd273938f30f3bb961943289c77aa5d38f5773b41a5f47fdaa69aaae6f92c6</t>
+          <t>0xb38a3cc2cf9c03f99487ec03657f937b47155f02bc75d79ffc33db76f98a69a6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -978,22 +962,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11.52135</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.6513</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>PSV Eindhoven -3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1003,27 +987,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs SC Telstar</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x8a99a50823ade222f81f1405d35b66126a5baec6c8557587d907d6fc42ee8959</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19403940</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1048,17 +1032,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786133357</t>
+          <t>1786142904</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>7.677543</t>
+          <t>34.011365</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,7 +1059,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x1fcc69e05756a9495c54cf92ec95cc3fa98841963ff82dbc95bde1118d0e88d6</t>
+          <t>0x7a20466d35539c024b1d077354a8e89cf90472d7db1127f1ec7682095c931015</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1090,22 +1074,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13.75169</t>
+          <t>9.70945</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -3</t>
+          <t>PSV Eindhoven -2.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1130,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786132692</t>
+          <t>1786142904</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>41.514536</t>
+          <t>21.339451</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,31 +1171,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x633e302e1f4a45e6cae190310048fc5640fdefddf9379c3100fb1c66a99ed226</t>
+          <t>0x3e2fa39473c09803be951522f0cce2a88e71007867e0d6a0ae033e851124bc38</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>855.42</t>
+          <t>367.52999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1219,27 +1211,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1256,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786129763</t>
+          <t>1786142696</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1555.309091</t>
+          <t>624.25476</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,28 +1283,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x0630cb5bb6cb2cff5cff3d307163d367059153070ce4cc710f35aa8d5c0c6825</t>
+          <t>0xd9c75ae7cbf7ebba9529c5699532d10d62802be6aac9ffc45052aa92cc35d72d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1323,27 +1315,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x4882e1214422a29af689a209790d0484e91067d78c514ab50b9376875ef6c6da</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1368,17 +1360,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786129750</t>
+          <t>1786142027</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>132.545455</t>
+          <t>50.64684</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,7 +1387,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x7935024ab7987fd550aa17e789e9bdc95e2fbd51b52763713f00cf3fdfce8bdd</t>
+          <t>0x417760c1d35fd131f695db2c7f2e8400a5d3d5d5903b79ac1ca222a5a30d0134</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1403,23 +1395,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>14.33</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -2</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1427,27 +1427,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xd9978e221ac5eb1139faeeefdedfd12ffe6f1986a602f6669e76abce9bb9067d</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1472,17 +1472,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786129738</t>
+          <t>1786140016</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>26.054545</t>
+          <t>2.101545</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x2b5a8f7ff44e3e83441016e9d07c7203d32fcbd029be82f693028e41ea14167e</t>
+          <t>0x16fd77e28d16ec069fe859b1ad63a1ce956b06b6136d6ac68ccdb02be6b3c94c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1510,17 +1510,17 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.20999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.8475</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1531,27 +1531,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x656b05c8c9e0a63d26fa6dcc4ddf398d649bc013ac423819523cf94211567658</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786129725</t>
+          <t>1786136525</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>11.290891</t>
+          <t>11.79941</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x9be5cfaca91d026b377dc51c41481c7420f402caa117cd1a71bf175f81b8ba3f</t>
+          <t>0xd3c8bb8d02330d8124e995d21959103edcd0baaa6289b159970a2225912e418d</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1614,17 +1614,17 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1635,27 +1635,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1680,17 +1680,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786129713</t>
+          <t>1786135338</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>31.436364</t>
+          <t>4.792453</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xffdb31c98c0c9e42bd2a3a4ac8c08c4dddf1bac9229455355ddf0f61eda11f5f</t>
+          <t>0xbdbdd9823b5c0238c109c0b23805ef0ff9a61aa34409f875e76398a0a7d6a460</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1718,17 +1718,17 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>52.93</t>
+          <t>48.04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1739,27 +1739,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786129699</t>
+          <t>1786135338</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>96.236364</t>
+          <t>181.283019</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x171c10e2c280f22ecd4a761a066bbcf7603ce72eb3464dbacf9b961ad202fb59</t>
+          <t>0x6e5e8a0fc2f92f97555f424e1454c8c7768aee012cd36da5c6482cae7684c76a</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1819,23 +1819,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>215.36</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1843,27 +1851,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1888,17 +1896,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786129686</t>
+          <t>1786135337</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>391.563636</t>
+          <t>7.577358</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,7 +1923,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x5ea684350a1a0b65d0f38be341db1516c1df4fe66d544944688193d0c3e3f0de</t>
+          <t>0xe9b4cf790ad6491c958a9df98bf381066cbab97000c72aaa03df184df175418c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1930,22 +1938,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>495.02</t>
+          <t>8.36113</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>PSV Eindhoven -3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1955,27 +1963,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2000,17 +2008,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786129356</t>
+          <t>1786135296</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>995.015075</t>
+          <t>25.241147</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,12 +2035,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x1a61ba580443c208fcf8a35afa56d0df4aaad017c49874a664c65a6551ec7d84</t>
+          <t>0xadbd273938f30f3bb961943289c77aa5d38f5773b41a5f47fdaa69aaae6f92c6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2042,22 +2050,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>495.02</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.6513</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2067,27 +2075,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x8a99a50823ade222f81f1405d35b66126a5baec6c8557587d907d6fc42ee8959</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2112,17 +2120,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786129323</t>
+          <t>1786133357</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>995.015075</t>
+          <t>7.677543</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,7 +2147,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xbc4a52ef8f6d90db800339bd0fdc45e1e4887cc29721741fa364564427cebc93</t>
+          <t>0x1fcc69e05756a9495c54cf92ec95cc3fa98841963ff82dbc95bde1118d0e88d6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2154,22 +2162,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>13.75169</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>PSV Eindhoven -3</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2179,27 +2187,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2224,17 +2232,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786129297</t>
+          <t>1786132692</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>97.507538</t>
+          <t>41.514536</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,7 +2259,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x009e27d36e3bfb01593b611eb8138842f7baf97d375a4302c10337f4fa65da7a</t>
+          <t>0x633e302e1f4a45e6cae190310048fc5640fdefddf9379c3100fb1c66a99ed226</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2259,19 +2267,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>855.42</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2279,11 +2283,7 @@
           <t>Under/Over (4.5)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786128259</t>
+          <t>1786129763</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>152.897196</t>
+          <t>1555.309091</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x987370b50d0502b7fd566ef6bb2bf38112c25bf81110ad0b1926b02ffd8ccd9d</t>
+          <t>0x0630cb5bb6cb2cff5cff3d307163d367059153070ce4cc710f35aa8d5c0c6825</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2371,31 +2371,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2403,27 +2395,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2448,17 +2440,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786127657</t>
+          <t>1786129750</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>5.94717</t>
+          <t>132.545455</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,7 +2467,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x38207556aceeaaa6ba9394fe5b398b808e1d67e0bba9c3b0fa61a88d5c5aebb7</t>
+          <t>0x7935024ab7987fd550aa17e789e9bdc95e2fbd51b52763713f00cf3fdfce8bdd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2483,31 +2475,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21.40562</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0737</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Fortuna Sittard</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2515,27 +2499,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2560,17 +2544,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786126212</t>
+          <t>1786129738</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>290.245695</t>
+          <t>26.054545</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2587,7 +2571,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x83a78ff6339d485633ea010240dad1c0ad7f4a30a2628cd7eb01ab0370275ddc</t>
+          <t>0x2b5a8f7ff44e3e83441016e9d07c7203d32fcbd029be82f693028e41ea14167e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2598,17 +2582,17 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4.76023</t>
+          <t>6.20999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2634,7 +2618,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2664,7 +2648,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786125622</t>
+          <t>1786129725</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2674,7 +2658,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>10.292389</t>
+          <t>11.290891</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2691,28 +2675,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x5630ba52ae08208c16f996b3fc5f0ab29f63363f75b764a890d5196f1a24e9b9</t>
+          <t>0x9be5cfaca91d026b377dc51c41481c7420f402caa117cd1a71bf175f81b8ba3f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x6e70489F443F69f1a091af8509f0b99338460D39</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>249.99999</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2738,7 +2722,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2768,7 +2752,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786125585</t>
+          <t>1786129713</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2778,7 +2762,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>469.483549</t>
+          <t>31.436364</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2795,28 +2779,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x272659eb9c2a40b218a61bdb98731190ae92104b09c8c08096e7cacce4e2dc79</t>
+          <t>0xffdb31c98c0c9e42bd2a3a4ac8c08c4dddf1bac9229455355ddf0f61eda11f5f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>52.93</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2842,7 +2826,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2872,7 +2856,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786125525</t>
+          <t>1786129699</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2882,7 +2866,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>9.389671</t>
+          <t>96.236364</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,28 +2883,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xc8538d15c53a4c377da962db1d0193aab217862d8ad9ac90a3999b587e2a1c53</t>
+          <t>0x171c10e2c280f22ecd4a761a066bbcf7603ce72eb3464dbacf9b961ad202fb59</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>76.29599</t>
+          <t>215.36</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5312</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2946,7 +2930,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2976,7 +2960,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786125507</t>
+          <t>1786129686</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2986,7 +2970,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>143.615981</t>
+          <t>391.563636</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,7 +2987,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xcb1bccb079df818106a903bda81def1d78bea048113133314cb9b5de80505b9a</t>
+          <t>0x5ea684350a1a0b65d0f38be341db1516c1df4fe66d544944688193d0c3e3f0de</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3018,47 +3002,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4.14001</t>
+          <t>495.02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3088,7 +3072,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786124259</t>
+          <t>1786129356</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3098,7 +3082,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10.894763</t>
+          <t>995.015075</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3115,7 +3099,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x7b5620344652130ca3f87e52b00289e9ee38aab6c426c0e9cd693b417361526c</t>
+          <t>0x1a61ba580443c208fcf8a35afa56d0df4aaad017c49874a664c65a6551ec7d84</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3130,47 +3114,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>495.02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3200,7 +3184,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786124259</t>
+          <t>1786129323</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3210,7 +3194,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>157.894737</t>
+          <t>995.015075</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3227,7 +3211,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xdc6c27f0359af82e276a61c449bef19ee4c2778a601eecfac8b0ae278c4fed31</t>
+          <t>0xbc4a52ef8f6d90db800339bd0fdc45e1e4887cc29721741fa364564427cebc93</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3242,47 +3226,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.3787</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3312,7 +3296,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786124228</t>
+          <t>1786129297</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3322,7 +3306,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>168.844884</t>
+          <t>97.507538</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3339,7 +3323,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xb740a9883984f2d057b5bd144c80df89d3be4972b6802619769be156582f7530</t>
+          <t>0x009e27d36e3bfb01593b611eb8138842f7baf97d375a4302c10337f4fa65da7a</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3354,47 +3338,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>56.08</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3725</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3424,7 +3408,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786123222</t>
+          <t>1786128259</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3434,7 +3418,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>150.550336</t>
+          <t>152.897196</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3451,12 +3435,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x1eb675eb4dddff6e46c7fe87ea19a03c7d5274c16759609d8d9cad3c46312d55</t>
+          <t>0x987370b50d0502b7fd566ef6bb2bf38112c25bf81110ad0b1926b02ffd8ccd9d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3466,22 +3450,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>PSV Eindhoven -3</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3491,27 +3475,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3536,17 +3520,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786123213</t>
+          <t>1786127657</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>14.349776</t>
+          <t>5.94717</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3563,23 +3547,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
+          <t>0x38207556aceeaaa6ba9394fe5b398b808e1d67e0bba9c3b0fa61a88d5c5aebb7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21.40562</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.0737</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3587,7 +3575,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3595,27 +3587,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
+          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3640,17 +3632,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786122007</t>
+          <t>1786126212</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>13.62862</t>
+          <t>290.245695</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3667,23 +3659,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
+          <t>0x83a78ff6339d485633ea010240dad1c0ad7f4a30a2628cd7eb01ab0370275ddc</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>4.76023</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4563</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3744,7 +3736,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786117951</t>
+          <t>1786125622</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3754,7 +3746,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>43.769863</t>
+          <t>10.292389</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3771,28 +3763,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
+          <t>0x5630ba52ae08208c16f996b3fc5f0ab29f63363f75b764a890d5196f1a24e9b9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+          <t>0x6e70489F443F69f1a091af8509f0b99338460D39</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>249.99999</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.6812</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3818,7 +3810,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3848,7 +3840,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786116835</t>
+          <t>1786125585</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3858,7 +3850,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.467861</t>
+          <t>469.483549</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3875,28 +3867,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
+          <t>0x272659eb9c2a40b218a61bdb98731190ae92104b09c8c08096e7cacce4e2dc79</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3907,27 +3899,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3952,17 +3944,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786115830</t>
+          <t>1786125525</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.389671</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,28 +3971,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
+          <t>0xc8538d15c53a4c377da962db1d0193aab217862d8ad9ac90a3999b587e2a1c53</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.36999</t>
+          <t>76.29599</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.5312</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4011,27 +4003,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4056,17 +4048,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786115829</t>
+          <t>1786125507</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.985493</t>
+          <t>143.615981</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4083,23 +4075,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
+          <t>0xcb1bccb079df818106a903bda81def1d78bea048113133314cb9b5de80505b9a</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>4.14001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4107,7 +4103,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4115,27 +4115,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786115827</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1.463754</t>
+          <t>10.894763</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4187,12 +4187,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
+          <t>0x7b5620344652130ca3f87e52b00289e9ee38aab6c426c0e9cd693b417361526c</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786115129</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>13.559322</t>
+          <t>157.894737</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4299,36 +4299,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
+          <t>0xdc6c27f0359af82e276a61c449bef19ee4c2778a601eecfac8b0ae278c4fed31</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.3787</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -4346,7 +4354,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4376,7 +4384,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786115128</t>
+          <t>1786124228</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4386,7 +4394,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>9.852217</t>
+          <t>168.844884</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4403,12 +4411,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
+          <t>0xb740a9883984f2d057b5bd144c80df89d3be4972b6802619769be156582f7530</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4418,12 +4426,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>56.08</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4488,7 +4496,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786123222</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4498,7 +4506,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>85.387755</t>
+          <t>150.550336</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4515,36 +4523,44 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
+          <t>0x1eb675eb4dddff6e46c7fe87ea19a03c7d5274c16759609d8d9cad3c46312d55</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>177.44126</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -4562,7 +4578,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4592,7 +4608,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786123213</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4602,7 +4618,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>350.501254</t>
+          <t>14.349776</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4619,27 +4635,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
+          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4647,11 +4659,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4659,27 +4667,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4704,17 +4712,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786111515</t>
+          <t>1786122007</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.698514</t>
+          <t>13.62862</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,39 +4739,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
+          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.4563</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4771,27 +4771,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4816,17 +4816,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786105696</t>
+          <t>1786117951</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>16.985121</t>
+          <t>43.769863</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4843,39 +4843,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
+          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.49993</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.9463</t>
+          <t>1.6812</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Over 0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4883,7 +4875,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4893,12 +4885,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4928,7 +4920,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786104752</t>
+          <t>1786116835</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4938,7 +4930,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>4.75554</t>
+          <t>1.467861</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4955,39 +4947,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
+          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5.99989</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Over 0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4995,27 +4979,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5040,17 +5024,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786104743</t>
+          <t>1786115830</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>6.34909</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5067,28 +5051,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.36999</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5099,27 +5083,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5144,17 +5128,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786102413</t>
+          <t>1786115829</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>3.706122</t>
+          <t>1.985493</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5171,28 +5155,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.2212</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5203,27 +5187,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5248,17 +5232,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786102412</t>
+          <t>1786115827</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>4.519774</t>
+          <t>1.463754</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5275,31 +5259,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5307,27 +5299,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5352,17 +5344,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786102410</t>
+          <t>1786115129</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2.416918</t>
+          <t>13.559322</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5379,28 +5371,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.5075</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5411,27 +5403,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5456,17 +5448,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786102409</t>
+          <t>1786115128</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>5.128205</t>
+          <t>9.852217</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5483,12 +5475,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5498,12 +5490,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5568,7 +5560,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786096483</t>
+          <t>1786115115</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5578,7 +5570,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>151.554007</t>
+          <t>85.387755</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5595,62 +5587,54 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>177.44126</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5680,7 +5664,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786095316</t>
+          <t>1786115115</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5690,7 +5674,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>15.69338</t>
+          <t>350.501254</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5707,12 +5691,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5722,22 +5706,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5747,27 +5731,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5792,17 +5776,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786086947</t>
+          <t>1786111515</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>503.272727</t>
+          <t>1.698514</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5819,12 +5803,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5834,12 +5818,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20.39624</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5849,7 +5833,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5859,27 +5843,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5904,17 +5888,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786082661</t>
+          <t>1786105696</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>54.389973</t>
+          <t>16.985121</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5931,31 +5915,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>4.49993</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.9463</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5963,27 +5955,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6008,17 +6000,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786104752</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>4.75554</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6035,31 +6027,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>5.99989</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.945</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6067,7 +6067,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6077,12 +6077,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786104743</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>6.34909</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6139,110 +6139,1182 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.6125</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1786102413</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>3.706122</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.2212</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1786102412</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>4.519774</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1786102410</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2.416918</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.195</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19403947</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1786102409</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1786207500</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>5.128205</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>54.37</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1786096483</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>151.554007</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1786095316</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>15.69338</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1786086947</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>503.272727</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>20.39624</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.375</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1786082661</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>54.389973</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>14.19</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.5675</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1786076493</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>25.004405</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V64"/>
+  <dimension ref="A1:V71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x7eaedb8f4752259366867abf771d84c0d99e47010227fd51681abeb60b48411b</t>
+          <t>0xb3bc0ed4c483bee8be05ae8fc496bbe64b2b2dad9597773c67ca17df236c46c6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.1638</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xc998a4ccb6265ea2336288383810c1b769d49949dbefbe46fcd473372116b82c</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786146812</t>
+          <t>1786158954</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>6.10687</t>
+          <t>10.094545</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +643,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xc17004473d1c14453448f29404ac7988d663c0f1eac3d80503d006f04db8d7a6</t>
+          <t>0x73f8172d3365445d5d6481e5b681390927b19eba83d829e34347ddf969f4d3aa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3725</t>
+          <t>1.0925</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x836ea569e8bb4a65752149e8c476f1184a85ddb5570c5106624ba137f9a0a2d5</t>
+          <t>0x70ad3839eaf0acb3b01efaf7fbad4dc4e6d59e9cba36c93a59ba571f812853a5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786146806</t>
+          <t>1786158954</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.684564</t>
+          <t>14.486486</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x88de27964fdb5afcbdf9d01c80c57e6ae6197056927b86aeb5d5e9260acc2828</t>
+          <t>0x49223560553949c798e427bb609beb8d54b408bb92fac667c5e805a35d272dd8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -755,12 +763,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.0775</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -771,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xca6f32a50927cbde2cb395d95e723ecf21a4b1811b744369dad7d460f821dd6d</t>
+          <t>0x9a0bc510c3953793967123d2592a887e55b2c7b4d336100e6a3528497b495765</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786146805</t>
+          <t>1786158687</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>12.903226</t>
+          <t>1.687764</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,12 +851,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x7c22fadfd0e1f902b93e750db5984c247214d30b4fe99214ef93a9e2ad497877</t>
+          <t>0x52a28d048aabdc20f81aa23618c25399119d945b7c7afae212c263d469fce473</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -859,12 +867,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1625</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -875,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PEC Zwolle vs Ajax Amsterdam</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xdd44346ee5e92ddeb574c7b372f2f6e8cfcd74de2a5309e9003a1550bcc12ab0</t>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19403941</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786146805</t>
+          <t>1786158626</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>6.153846</t>
+          <t>2.439024</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,12 +955,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xb38a3cc2cf9c03f99487ec03657f937b47155f02bc75d79ffc33db76f98a69a6</t>
+          <t>0x654ee8bcaf6b781089890f7528b8d264645cbb382b68a3166b49f74e9e50d5fa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -962,22 +970,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11.52135</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -3</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -987,27 +995,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0x700c0930687f6c1dc816f7af554f65cf4b2844ee77830f992d4a731c0df2564f</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1032,17 +1040,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786142904</t>
+          <t>1786158491</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>34.011365</t>
+          <t>1.033592</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,12 +1067,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x7a20466d35539c024b1d077354a8e89cf90472d7db1127f1ec7682095c931015</t>
+          <t>0x38b906d6e5d0de2738537770dc05e6338898a8b937e89cbc914ae6e75513308b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1074,22 +1082,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.70945</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -2.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1099,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0x2ea149fa9b38b9090f5b506ae3dca75e0788add16a579f9705e6feb502e84868</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1144,17 +1152,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786142904</t>
+          <t>1786158491</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>21.339451</t>
+          <t>1.033592</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,39 +1179,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x3e2fa39473c09803be951522f0cce2a88e71007867e0d6a0ae033e851124bc38</t>
+          <t>0x598f4044b8d7101954a12cfb6a028285705b009e647d167cb12be8cc1aa8c433</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>367.52999</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1211,27 +1211,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0x9455b4a5e4ea76ab5db55d0b29615eeae7a6c51e3bc31b5c6b0ed2395a188551</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786142696</t>
+          <t>1786158381</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>624.25476</t>
+          <t>1.781719</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,28 +1283,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xd9c75ae7cbf7ebba9529c5699532d10d62802be6aac9ffc45052aa92cc35d72d</t>
+          <t>0x7eaedb8f4752259366867abf771d84c0d99e47010227fd51681abeb60b48411b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.1638</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x4882e1214422a29af689a209790d0484e91067d78c514ab50b9376875ef6c6da</t>
+          <t>0xc998a4ccb6265ea2336288383810c1b769d49949dbefbe46fcd473372116b82c</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786142027</t>
+          <t>1786146812</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>50.64684</t>
+          <t>6.10687</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,39 +1387,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x417760c1d35fd131f695db2c7f2e8400a5d3d5d5903b79ac1ca222a5a30d0134</t>
+          <t>0xc17004473d1c14453448f29404ac7988d663c0f1eac3d80503d006f04db8d7a6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -2</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1427,27 +1419,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xd9978e221ac5eb1139faeeefdedfd12ffe6f1986a602f6669e76abce9bb9067d</t>
+          <t>0x836ea569e8bb4a65752149e8c476f1184a85ddb5570c5106624ba137f9a0a2d5</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1472,17 +1464,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786140016</t>
+          <t>1786146806</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.101545</t>
+          <t>2.684564</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,28 +1491,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x16fd77e28d16ec069fe859b1ad63a1ce956b06b6136d6ac68ccdb02be6b3c94c</t>
+          <t>0x88de27964fdb5afcbdf9d01c80c57e6ae6197056927b86aeb5d5e9260acc2828</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.8475</t>
+          <t>1.0775</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1531,27 +1523,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs SC Telstar</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x656b05c8c9e0a63d26fa6dcc4ddf398d649bc013ac423819523cf94211567658</t>
+          <t>0xca6f32a50927cbde2cb395d95e723ecf21a4b1811b744369dad7d460f821dd6d</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19403940</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1576,17 +1568,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786136525</t>
+          <t>1786146805</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>11.79941</t>
+          <t>12.903226</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,28 +1595,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xd3c8bb8d02330d8124e995d21959103edcd0baaa6289b159970a2225912e418d</t>
+          <t>0x7c22fadfd0e1f902b93e750db5984c247214d30b4fe99214ef93a9e2ad497877</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.1625</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1635,27 +1627,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>PEC Zwolle vs Ajax Amsterdam</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Ajax Amsterdam</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
+          <t>0xdd44346ee5e92ddeb574c7b372f2f6e8cfcd74de2a5309e9003a1550bcc12ab0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403941</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1680,17 +1672,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786135338</t>
+          <t>1786146805</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>4.792453</t>
+          <t>6.153846</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,7 +1699,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xbdbdd9823b5c0238c109c0b23805ef0ff9a61aa34409f875e76398a0a7d6a460</t>
+          <t>0xb38a3cc2cf9c03f99487ec03657f937b47155f02bc75d79ffc33db76f98a69a6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1715,23 +1707,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>11.52135</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786135338</t>
+          <t>1786142904</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>181.283019</t>
+          <t>34.011365</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x6e5e8a0fc2f92f97555f424e1454c8c7768aee012cd36da5c6482cae7684c76a</t>
+          <t>0x7a20466d35539c024b1d077354a8e89cf90472d7db1127f1ec7682095c931015</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>9.70945</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -3</t>
+          <t>PSV Eindhoven -2.5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786135337</t>
+          <t>1786142904</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>7.577358</t>
+          <t>21.339451</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xe9b4cf790ad6491c958a9df98bf381066cbab97000c72aaa03df184df175418c</t>
+          <t>0x3e2fa39473c09803be951522f0cce2a88e71007867e0d6a0ae033e851124bc38</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.36113</t>
+          <t>367.52999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -3</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1963,27 +1963,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2008,17 +2008,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786135296</t>
+          <t>1786142696</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>25.241147</t>
+          <t>624.25476</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,27 +2035,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xadbd273938f30f3bb961943289c77aa5d38f5773b41a5f47fdaa69aaae6f92c6</t>
+          <t>0xd9c75ae7cbf7ebba9529c5699532d10d62802be6aac9ffc45052aa92cc35d72d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.6513</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2063,11 +2059,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>NEC Nijmegen</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2075,27 +2067,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs SC Telstar</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x8a99a50823ade222f81f1405d35b66126a5baec6c8557587d907d6fc42ee8959</t>
+          <t>0x4882e1214422a29af689a209790d0484e91067d78c514ab50b9376875ef6c6da</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19403940</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2120,17 +2112,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786133357</t>
+          <t>1786142027</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>7.677543</t>
+          <t>50.64684</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,7 +2139,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x1fcc69e05756a9495c54cf92ec95cc3fa98841963ff82dbc95bde1118d0e88d6</t>
+          <t>0x417760c1d35fd131f695db2c7f2e8400a5d3d5d5903b79ac1ca222a5a30d0134</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2162,22 +2154,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13.75169</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -3</t>
+          <t>PSV Eindhoven -2</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2202,7 +2194,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xd9978e221ac5eb1139faeeefdedfd12ffe6f1986a602f6669e76abce9bb9067d</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2232,7 +2224,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786132692</t>
+          <t>1786140016</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2242,7 +2234,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>41.514536</t>
+          <t>2.101545</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,7 +2251,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x633e302e1f4a45e6cae190310048fc5640fdefddf9379c3100fb1c66a99ed226</t>
+          <t>0x16fd77e28d16ec069fe859b1ad63a1ce956b06b6136d6ac68ccdb02be6b3c94c</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2270,17 +2262,17 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>855.42</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.8475</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2291,27 +2283,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x656b05c8c9e0a63d26fa6dcc4ddf398d649bc013ac423819523cf94211567658</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2336,17 +2328,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786129763</t>
+          <t>1786136525</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1555.309091</t>
+          <t>11.79941</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,7 +2355,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x0630cb5bb6cb2cff5cff3d307163d367059153070ce4cc710f35aa8d5c0c6825</t>
+          <t>0xd3c8bb8d02330d8124e995d21959103edcd0baaa6289b159970a2225912e418d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2374,17 +2366,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2395,27 +2387,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2440,17 +2432,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786129750</t>
+          <t>1786135338</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>132.545455</t>
+          <t>4.792453</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,7 +2459,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x7935024ab7987fd550aa17e789e9bdc95e2fbd51b52763713f00cf3fdfce8bdd</t>
+          <t>0xbdbdd9823b5c0238c109c0b23805ef0ff9a61aa34409f875e76398a0a7d6a460</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2478,17 +2470,17 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>14.33</t>
+          <t>48.04</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2499,27 +2491,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2544,17 +2536,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786129738</t>
+          <t>1786135338</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>26.054545</t>
+          <t>181.283019</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,7 +2563,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x2b5a8f7ff44e3e83441016e9d07c7203d32fcbd029be82f693028e41ea14167e</t>
+          <t>0x6e5e8a0fc2f92f97555f424e1454c8c7768aee012cd36da5c6482cae7684c76a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2579,23 +2571,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6.20999</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2603,27 +2603,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2648,17 +2648,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786129725</t>
+          <t>1786135337</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>11.290891</t>
+          <t>7.577358</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2675,7 +2675,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x9be5cfaca91d026b377dc51c41481c7420f402caa117cd1a71bf175f81b8ba3f</t>
+          <t>0xe9b4cf790ad6491c958a9df98bf381066cbab97000c72aaa03df184df175418c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2683,23 +2683,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>8.36113</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2707,27 +2715,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2752,17 +2760,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786129713</t>
+          <t>1786135296</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>31.436364</t>
+          <t>25.241147</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,31 +2787,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xffdb31c98c0c9e42bd2a3a4ac8c08c4dddf1bac9229455355ddf0f61eda11f5f</t>
+          <t>0xadbd273938f30f3bb961943289c77aa5d38f5773b41a5f47fdaa69aaae6f92c6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.93</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.6513</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2811,27 +2827,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x8a99a50823ade222f81f1405d35b66126a5baec6c8557587d907d6fc42ee8959</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2856,17 +2872,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786129699</t>
+          <t>1786133357</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>96.236364</t>
+          <t>7.677543</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2883,7 +2899,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x171c10e2c280f22ecd4a761a066bbcf7603ce72eb3464dbacf9b961ad202fb59</t>
+          <t>0x1fcc69e05756a9495c54cf92ec95cc3fa98841963ff82dbc95bde1118d0e88d6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2891,23 +2907,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>215.36</t>
+          <t>13.75169</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2915,27 +2939,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2960,17 +2984,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786129686</t>
+          <t>1786132692</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>391.563636</t>
+          <t>41.514536</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2987,7 +3011,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x5ea684350a1a0b65d0f38be341db1516c1df4fe66d544944688193d0c3e3f0de</t>
+          <t>0x633e302e1f4a45e6cae190310048fc5640fdefddf9379c3100fb1c66a99ed226</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2995,19 +3019,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>495.02</t>
+          <t>855.42</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3015,11 +3035,7 @@
           <t>Under/Over (4.5)</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3072,7 +3088,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786129356</t>
+          <t>1786129763</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3082,7 +3098,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>995.015075</t>
+          <t>1555.309091</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3099,7 +3115,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x1a61ba580443c208fcf8a35afa56d0df4aaad017c49874a664c65a6551ec7d84</t>
+          <t>0x0630cb5bb6cb2cff5cff3d307163d367059153070ce4cc710f35aa8d5c0c6825</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3107,19 +3123,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>495.02</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3127,11 +3139,7 @@
           <t>Under/Over (4.5)</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3184,7 +3192,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786129323</t>
+          <t>1786129750</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3194,7 +3202,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>995.015075</t>
+          <t>132.545455</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3211,7 +3219,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xbc4a52ef8f6d90db800339bd0fdc45e1e4887cc29721741fa364564427cebc93</t>
+          <t>0x7935024ab7987fd550aa17e789e9bdc95e2fbd51b52763713f00cf3fdfce8bdd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3219,19 +3227,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3239,11 +3243,7 @@
           <t>Under/Over (4.5)</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786129297</t>
+          <t>1786129738</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>97.507538</t>
+          <t>26.054545</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3323,7 +3323,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x009e27d36e3bfb01593b611eb8138842f7baf97d375a4302c10337f4fa65da7a</t>
+          <t>0x2b5a8f7ff44e3e83441016e9d07c7203d32fcbd029be82f693028e41ea14167e</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3331,19 +3331,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>6.20999</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3351,11 +3347,7 @@
           <t>Under/Over (4.5)</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3408,7 +3400,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786128259</t>
+          <t>1786129725</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3418,7 +3410,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>152.897196</t>
+          <t>11.290891</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3435,7 +3427,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x987370b50d0502b7fd566ef6bb2bf38112c25bf81110ad0b1926b02ffd8ccd9d</t>
+          <t>0x9be5cfaca91d026b377dc51c41481c7420f402caa117cd1a71bf175f81b8ba3f</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3443,31 +3435,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3475,27 +3459,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3520,17 +3504,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786127657</t>
+          <t>1786129713</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>5.94717</t>
+          <t>31.436364</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3547,7 +3531,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x38207556aceeaaa6ba9394fe5b398b808e1d67e0bba9c3b0fa61a88d5c5aebb7</t>
+          <t>0xffdb31c98c0c9e42bd2a3a4ac8c08c4dddf1bac9229455355ddf0f61eda11f5f</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3555,31 +3539,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21.40562</t>
+          <t>52.93</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.0737</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Fortuna Sittard</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3587,27 +3563,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3632,17 +3608,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786126212</t>
+          <t>1786129699</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>290.245695</t>
+          <t>96.236364</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3659,7 +3635,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x83a78ff6339d485633ea010240dad1c0ad7f4a30a2628cd7eb01ab0370275ddc</t>
+          <t>0x171c10e2c280f22ecd4a761a066bbcf7603ce72eb3464dbacf9b961ad202fb59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3670,17 +3646,17 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.76023</t>
+          <t>215.36</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3706,7 +3682,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3736,7 +3712,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786125622</t>
+          <t>1786129686</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3746,7 +3722,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>10.292389</t>
+          <t>391.563636</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3763,36 +3739,44 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x5630ba52ae08208c16f996b3fc5f0ab29f63363f75b764a890d5196f1a24e9b9</t>
+          <t>0x5ea684350a1a0b65d0f38be341db1516c1df4fe66d544944688193d0c3e3f0de</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x6e70489F443F69f1a091af8509f0b99338460D39</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>249.99999</t>
+          <t>495.02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -3810,7 +3794,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3840,7 +3824,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786125585</t>
+          <t>1786129356</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3850,7 +3834,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>469.483549</t>
+          <t>995.015075</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3867,36 +3851,44 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x272659eb9c2a40b218a61bdb98731190ae92104b09c8c08096e7cacce4e2dc79</t>
+          <t>0x1a61ba580443c208fcf8a35afa56d0df4aaad017c49874a664c65a6551ec7d84</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>495.02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -3914,7 +3906,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3944,7 +3936,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786125525</t>
+          <t>1786129323</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3954,7 +3946,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>9.389671</t>
+          <t>995.015075</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3971,36 +3963,44 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xc8538d15c53a4c377da962db1d0193aab217862d8ad9ac90a3999b587e2a1c53</t>
+          <t>0xbc4a52ef8f6d90db800339bd0fdc45e1e4887cc29721741fa364564427cebc93</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>76.29599</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5312</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786125507</t>
+          <t>1786129297</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>143.615981</t>
+          <t>97.507538</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4075,7 +4075,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xcb1bccb079df818106a903bda81def1d78bea048113133314cb9b5de80505b9a</t>
+          <t>0x009e27d36e3bfb01593b611eb8138842f7baf97d375a4302c10337f4fa65da7a</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4090,47 +4090,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.14001</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786124259</t>
+          <t>1786128259</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>10.894763</t>
+          <t>152.897196</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x7b5620344652130ca3f87e52b00289e9ee38aab6c426c0e9cd693b417361526c</t>
+          <t>0x987370b50d0502b7fd566ef6bb2bf38112c25bf81110ad0b1926b02ffd8ccd9d</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4202,22 +4202,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven -3</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4227,27 +4227,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4272,17 +4272,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786124259</t>
+          <t>1786127657</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>157.894737</t>
+          <t>5.94717</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4299,7 +4299,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xdc6c27f0359af82e276a61c449bef19ee4c2778a601eecfac8b0ae278c4fed31</t>
+          <t>0x38207556aceeaaa6ba9394fe5b398b808e1d67e0bba9c3b0fa61a88d5c5aebb7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>21.40562</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.3787</t>
+          <t>1.0737</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4339,27 +4339,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4384,17 +4384,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786124228</t>
+          <t>1786126212</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>168.844884</t>
+          <t>290.245695</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xb740a9883984f2d057b5bd144c80df89d3be4972b6802619769be156582f7530</t>
+          <t>0x83a78ff6339d485633ea010240dad1c0ad7f4a30a2628cd7eb01ab0370275ddc</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4419,54 +4419,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>56.08</t>
+          <t>4.76023</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.3725</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4496,7 +4488,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786123222</t>
+          <t>1786125622</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4506,7 +4498,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>150.550336</t>
+          <t>10.292389</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4523,39 +4515,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x1eb675eb4dddff6e46c7fe87ea19a03c7d5274c16759609d8d9cad3c46312d55</t>
+          <t>0x5630ba52ae08208c16f996b3fc5f0ab29f63363f75b764a890d5196f1a24e9b9</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x6e70489F443F69f1a091af8509f0b99338460D39</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>249.99999</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4578,7 +4562,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4608,7 +4592,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786123213</t>
+          <t>1786125585</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4618,7 +4602,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>14.349776</t>
+          <t>469.483549</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4635,28 +4619,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
+          <t>0x272659eb9c2a40b218a61bdb98731190ae92104b09c8c08096e7cacce4e2dc79</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4682,7 +4666,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4712,7 +4696,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786122007</t>
+          <t>1786125525</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4722,7 +4706,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>13.62862</t>
+          <t>9.389671</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4739,28 +4723,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
+          <t>0xc8538d15c53a4c377da962db1d0193aab217862d8ad9ac90a3999b587e2a1c53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>76.29599</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.4563</t>
+          <t>1.5312</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4786,7 +4770,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4816,7 +4800,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786117951</t>
+          <t>1786125507</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4826,7 +4810,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>43.769863</t>
+          <t>143.615981</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4843,31 +4827,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
+          <t>0xcb1bccb079df818106a903bda81def1d78bea048113133314cb9b5de80505b9a</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>4.14001</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.6812</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4890,7 +4882,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4920,7 +4912,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786116835</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4930,7 +4922,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1.467861</t>
+          <t>10.894763</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,23 +4939,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
+          <t>0x7b5620344652130ca3f87e52b00289e9ee38aab6c426c0e9cd693b417361526c</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4971,7 +4967,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4979,27 +4979,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5024,17 +5024,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786115830</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>157.894737</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,23 +5051,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
+          <t>0xdc6c27f0359af82e276a61c449bef19ee4c2778a601eecfac8b0ae278c4fed31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.36999</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.3787</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5075,7 +5079,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5083,27 +5091,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5128,17 +5136,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786115829</t>
+          <t>1786124228</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.985493</t>
+          <t>168.844884</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5155,23 +5163,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
+          <t>0xb740a9883984f2d057b5bd144c80df89d3be4972b6802619769be156582f7530</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>56.08</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5179,7 +5191,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5187,27 +5203,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5232,17 +5248,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786115827</t>
+          <t>1786123222</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1.463754</t>
+          <t>150.550336</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5259,12 +5275,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
+          <t>0x1eb675eb4dddff6e46c7fe87ea19a03c7d5274c16759609d8d9cad3c46312d55</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5274,12 +5290,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5289,32 +5305,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5344,7 +5360,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786115129</t>
+          <t>1786123213</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5354,7 +5370,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>13.559322</t>
+          <t>14.349776</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5371,28 +5387,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
+          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5418,7 +5434,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5448,7 +5464,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786115128</t>
+          <t>1786122007</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5458,7 +5474,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>9.852217</t>
+          <t>13.62862</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5475,62 +5491,54 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
+          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.4563</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5560,7 +5568,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786117951</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5570,7 +5578,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>85.387755</t>
+          <t>43.769863</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5587,28 +5595,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
+          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>177.44126</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.6812</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5634,7 +5642,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5664,7 +5672,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786116835</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5674,7 +5682,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>350.501254</t>
+          <t>1.467861</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5691,27 +5699,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
+          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5719,11 +5723,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5731,27 +5731,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5776,17 +5776,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786111515</t>
+          <t>1786115830</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1.698514</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5803,27 +5803,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
+          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>1.36999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5831,11 +5827,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5843,27 +5835,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5888,17 +5880,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786105696</t>
+          <t>1786115829</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>16.985121</t>
+          <t>1.985493</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5915,39 +5907,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
+          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4.49993</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.9463</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Over 0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5955,27 +5939,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6000,17 +5984,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786104752</t>
+          <t>1786115827</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>4.75554</t>
+          <t>1.463754</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6027,12 +6011,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
+          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6042,22 +6026,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5.99989</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6067,7 +6051,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6077,12 +6061,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6112,7 +6096,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786104743</t>
+          <t>1786115129</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6122,7 +6106,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>6.34909</t>
+          <t>13.559322</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6139,28 +6123,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.5075</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6171,27 +6155,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6216,17 +6200,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786102413</t>
+          <t>1786115128</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>3.706122</t>
+          <t>9.852217</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6243,31 +6227,39 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.2212</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6275,27 +6267,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6320,17 +6312,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786102412</t>
+          <t>1786115115</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>4.519774</t>
+          <t>85.387755</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6347,28 +6339,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>177.44126</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -6379,27 +6371,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6424,17 +6416,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786102410</t>
+          <t>1786115115</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2.416918</t>
+          <t>350.501254</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6451,15 +6443,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>1</t>
@@ -6467,15 +6463,19 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786102409</t>
+          <t>1786111515</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>5.128205</t>
+          <t>1.698514</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6555,12 +6555,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6595,27 +6595,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6640,17 +6640,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786096483</t>
+          <t>1786105696</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>151.554007</t>
+          <t>16.985121</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6667,12 +6667,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6682,22 +6682,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>4.49993</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.9463</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Over 0.5</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786095316</t>
+          <t>1786104752</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>15.69338</t>
+          <t>4.75554</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6779,12 +6779,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6794,22 +6794,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>5.99989</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.945</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 0.5</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786086947</t>
+          <t>1786104743</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>503.272727</t>
+          <t>6.34909</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6891,39 +6891,31 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>20.39624</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6931,27 +6923,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6976,17 +6968,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786082661</t>
+          <t>1786102413</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>54.389973</t>
+          <t>3.706122</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7003,28 +6995,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.2212</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -7050,7 +7042,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7080,7 +7072,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786102412</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7090,7 +7082,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>4.519774</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7107,23 +7099,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7139,27 +7131,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7184,17 +7176,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786102410</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>2.416918</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7211,110 +7203,870 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.195</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19403947</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1786102409</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1786207500</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>5.128205</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>54.37</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1786096483</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>151.554007</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1786095316</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>15.69338</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1786086947</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>503.272727</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>20.39624</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.375</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1786082661</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>54.389973</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>14.19</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.5675</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1786076493</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>25.004405</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V71"/>
+  <dimension ref="A1:V75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xb3bc0ed4c483bee8be05ae8fc496bbe64b2b2dad9597773c67ca17df236c46c6</t>
+          <t>0xe8ac9d951a75bfb5f85a9df2129b2402e3d7896e9994d96820f9c2abd9dfd94c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>8.59894</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -3</t>
+          <t>NEC Nijmegen -2</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0x1ad454c96c47b60c3469ca957e70ba1e03d07a5415f5e1d36eb27c71b1b71929</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786158954</t>
+          <t>1786162832</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>10.094545</t>
+          <t>29.148949</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x73f8172d3365445d5d6481e5b681390927b19eba83d829e34347ddf969f4d3aa</t>
+          <t>0xc2ff6b7ef5c4d6b1ae7fb27264146c018690220314bfbd5d9f754aed33050ad1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -654,17 +654,17 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.1787</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -690,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x70ad3839eaf0acb3b01efaf7fbad4dc4e6d59e9cba36c93a59ba571f812853a5</t>
+          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786158954</t>
+          <t>1786161973</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>14.486486</t>
+          <t>9.846154</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,31 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x49223560553949c798e427bb609beb8d54b408bb92fac667c5e805a35d272dd8</t>
+          <t>0x75f10c8c3b07bcf97178db485e61f1e964f7925053c699f8e7ae25fdef0517ba</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.1125</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -779,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x9a0bc510c3953793967123d2592a887e55b2c7b4d336100e6a3528497b495765</t>
+          <t>0x2fbec757a98798a9e344fdcfeba32267077a6f189c5785b7b423a7d4efc507cd</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786158687</t>
+          <t>1786161973</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.687764</t>
+          <t>35.288889</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,28 +859,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x52a28d048aabdc20f81aa23618c25399119d945b7c7afae212c263d469fce473</t>
+          <t>0xe31905b26a7e1536bf125b184f1294f656fa4f22b6e9fd739a0a032c4d321ce0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9.73576</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.1787</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -898,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786158626</t>
+          <t>1786161913</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.439024</t>
+          <t>54.46579</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,12 +963,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x654ee8bcaf6b781089890f7528b8d264645cbb382b68a3166b49f74e9e50d5fa</t>
+          <t>0xb3bc0ed4c483bee8be05ae8fc496bbe64b2b2dad9597773c67ca17df236c46c6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -970,22 +978,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>PSV Eindhoven -3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -995,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x700c0930687f6c1dc816f7af554f65cf4b2844ee77830f992d4a731c0df2564f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1048,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786158491</t>
+          <t>1786158954</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.033592</t>
+          <t>10.094545</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,39 +1075,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x38b906d6e5d0de2738537770dc05e6338898a8b937e89cbc914ae6e75513308b</t>
+          <t>0x73f8172d3365445d5d6481e5b681390927b19eba83d829e34347ddf969f4d3aa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.0925</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1107,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x2ea149fa9b38b9090f5b506ae3dca75e0788add16a579f9705e6feb502e84868</t>
+          <t>0x70ad3839eaf0acb3b01efaf7fbad4dc4e6d59e9cba36c93a59ba571f812853a5</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786158491</t>
+          <t>1786158954</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.033592</t>
+          <t>14.486486</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x598f4044b8d7101954a12cfb6a028285705b009e647d167cb12be8cc1aa8c433</t>
+          <t>0x49223560553949c798e427bb609beb8d54b408bb92fac667c5e805a35d272dd8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,12 +1190,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1211,27 +1211,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs SC Telstar</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x9455b4a5e4ea76ab5db55d0b29615eeae7a6c51e3bc31b5c6b0ed2395a188551</t>
+          <t>0x9a0bc510c3953793967123d2592a887e55b2c7b4d336100e6a3528497b495765</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19403940</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786158381</t>
+          <t>1786158687</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.781719</t>
+          <t>1.687764</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,12 +1283,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x7eaedb8f4752259366867abf771d84c0d99e47010227fd51681abeb60b48411b</t>
+          <t>0x52a28d048aabdc20f81aa23618c25399119d945b7c7afae212c263d469fce473</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.1638</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1315,27 +1315,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xc998a4ccb6265ea2336288383810c1b769d49949dbefbe46fcd473372116b82c</t>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786146812</t>
+          <t>1786158626</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>6.10687</t>
+          <t>2.439024</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,31 +1387,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xc17004473d1c14453448f29404ac7988d663c0f1eac3d80503d006f04db8d7a6</t>
+          <t>0x654ee8bcaf6b781089890f7528b8d264645cbb382b68a3166b49f74e9e50d5fa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3725</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1419,27 +1427,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x836ea569e8bb4a65752149e8c476f1184a85ddb5570c5106624ba137f9a0a2d5</t>
+          <t>0x700c0930687f6c1dc816f7af554f65cf4b2844ee77830f992d4a731c0df2564f</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1464,17 +1472,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786146806</t>
+          <t>1786158491</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.684564</t>
+          <t>1.033592</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,31 +1499,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x88de27964fdb5afcbdf9d01c80c57e6ae6197056927b86aeb5d5e9260acc2828</t>
+          <t>0x38b906d6e5d0de2738537770dc05e6338898a8b937e89cbc914ae6e75513308b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.0775</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1523,27 +1539,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xca6f32a50927cbde2cb395d95e723ecf21a4b1811b744369dad7d460f821dd6d</t>
+          <t>0x2ea149fa9b38b9090f5b506ae3dca75e0788add16a579f9705e6feb502e84868</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1568,17 +1584,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786146805</t>
+          <t>1786158491</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>12.903226</t>
+          <t>1.033592</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,28 +1611,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x7c22fadfd0e1f902b93e750db5984c247214d30b4fe99214ef93a9e2ad497877</t>
+          <t>0x598f4044b8d7101954a12cfb6a028285705b009e647d167cb12be8cc1aa8c433</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.1625</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1627,27 +1643,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PEC Zwolle vs Ajax Amsterdam</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xdd44346ee5e92ddeb574c7b372f2f6e8cfcd74de2a5309e9003a1550bcc12ab0</t>
+          <t>0x9455b4a5e4ea76ab5db55d0b29615eeae7a6c51e3bc31b5c6b0ed2395a188551</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19403941</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1672,17 +1688,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786146805</t>
+          <t>1786158381</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6.153846</t>
+          <t>1.781719</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,39 +1715,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xb38a3cc2cf9c03f99487ec03657f937b47155f02bc75d79ffc33db76f98a69a6</t>
+          <t>0x7eaedb8f4752259366867abf771d84c0d99e47010227fd51681abeb60b48411b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11.52135</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.1638</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1739,27 +1747,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xc998a4ccb6265ea2336288383810c1b769d49949dbefbe46fcd473372116b82c</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1784,17 +1792,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786142904</t>
+          <t>1786146812</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>34.011365</t>
+          <t>6.10687</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,39 +1819,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x7a20466d35539c024b1d077354a8e89cf90472d7db1127f1ec7682095c931015</t>
+          <t>0xc17004473d1c14453448f29404ac7988d663c0f1eac3d80503d006f04db8d7a6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9.70945</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1851,27 +1851,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0x836ea569e8bb4a65752149e8c476f1184a85ddb5570c5106624ba137f9a0a2d5</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786142904</t>
+          <t>1786146806</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>21.339451</t>
+          <t>2.684564</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,39 +1923,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x3e2fa39473c09803be951522f0cce2a88e71007867e0d6a0ae033e851124bc38</t>
+          <t>0x88de27964fdb5afcbdf9d01c80c57e6ae6197056927b86aeb5d5e9260acc2828</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>367.52999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.0775</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1963,27 +1955,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0xca6f32a50927cbde2cb395d95e723ecf21a4b1811b744369dad7d460f821dd6d</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2008,17 +2000,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786142696</t>
+          <t>1786146805</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>624.25476</t>
+          <t>12.903226</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,28 +2027,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xd9c75ae7cbf7ebba9529c5699532d10d62802be6aac9ffc45052aa92cc35d72d</t>
+          <t>0x7c22fadfd0e1f902b93e750db5984c247214d30b4fe99214ef93a9e2ad497877</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.1625</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2067,27 +2059,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>PEC Zwolle vs Ajax Amsterdam</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Ajax Amsterdam</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x4882e1214422a29af689a209790d0484e91067d78c514ab50b9376875ef6c6da</t>
+          <t>0xdd44346ee5e92ddeb574c7b372f2f6e8cfcd74de2a5309e9003a1550bcc12ab0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403941</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2112,17 +2104,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786142027</t>
+          <t>1786146805</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>50.64684</t>
+          <t>6.153846</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,7 +2131,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x417760c1d35fd131f695db2c7f2e8400a5d3d5d5903b79ac1ca222a5a30d0134</t>
+          <t>0xb38a3cc2cf9c03f99487ec03657f937b47155f02bc75d79ffc33db76f98a69a6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2154,22 +2146,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>11.52135</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -2</t>
+          <t>PSV Eindhoven -3</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2194,7 +2186,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xd9978e221ac5eb1139faeeefdedfd12ffe6f1986a602f6669e76abce9bb9067d</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2224,7 +2216,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786140016</t>
+          <t>1786142904</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2234,7 +2226,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.101545</t>
+          <t>34.011365</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x16fd77e28d16ec069fe859b1ad63a1ce956b06b6136d6ac68ccdb02be6b3c94c</t>
+          <t>0x7a20466d35539c024b1d077354a8e89cf90472d7db1127f1ec7682095c931015</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2259,23 +2251,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.70945</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.8475</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -2.5</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2283,27 +2283,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs SC Telstar</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x656b05c8c9e0a63d26fa6dcc4ddf398d649bc013ac423819523cf94211567658</t>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19403940</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2328,17 +2328,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786136525</t>
+          <t>1786142904</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>11.79941</t>
+          <t>21.339451</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2355,31 +2355,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xd3c8bb8d02330d8124e995d21959103edcd0baaa6289b159970a2225912e418d</t>
+          <t>0x3e2fa39473c09803be951522f0cce2a88e71007867e0d6a0ae033e851124bc38</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>367.52999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2387,27 +2395,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2432,17 +2440,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786135338</t>
+          <t>1786142696</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>4.792453</t>
+          <t>624.25476</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,28 +2467,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xbdbdd9823b5c0238c109c0b23805ef0ff9a61aa34409f875e76398a0a7d6a460</t>
+          <t>0xd9c75ae7cbf7ebba9529c5699532d10d62802be6aac9ffc45052aa92cc35d72d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2491,27 +2499,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
+          <t>0x4882e1214422a29af689a209790d0484e91067d78c514ab50b9376875ef6c6da</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2536,17 +2544,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786135338</t>
+          <t>1786142027</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>181.283019</t>
+          <t>50.64684</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2563,7 +2571,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x6e5e8a0fc2f92f97555f424e1454c8c7768aee012cd36da5c6482cae7684c76a</t>
+          <t>0x417760c1d35fd131f695db2c7f2e8400a5d3d5d5903b79ac1ca222a5a30d0134</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2578,22 +2586,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -3</t>
+          <t>PSV Eindhoven -2</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2618,7 +2626,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xd9978e221ac5eb1139faeeefdedfd12ffe6f1986a602f6669e76abce9bb9067d</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2648,7 +2656,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786135337</t>
+          <t>1786140016</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2658,7 +2666,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>7.577358</t>
+          <t>2.101545</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2675,7 +2683,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xe9b4cf790ad6491c958a9df98bf381066cbab97000c72aaa03df184df175418c</t>
+          <t>0x16fd77e28d16ec069fe859b1ad63a1ce956b06b6136d6ac68ccdb02be6b3c94c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2683,31 +2691,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.36113</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.8475</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2715,27 +2715,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0x656b05c8c9e0a63d26fa6dcc4ddf398d649bc013ac423819523cf94211567658</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786135296</t>
+          <t>1786136525</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>25.241147</t>
+          <t>11.79941</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,39 +2787,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xadbd273938f30f3bb961943289c77aa5d38f5773b41a5f47fdaa69aaae6f92c6</t>
+          <t>0xd3c8bb8d02330d8124e995d21959103edcd0baaa6289b159970a2225912e418d</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.6513</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NEC Nijmegen</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2827,27 +2819,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs SC Telstar</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x8a99a50823ade222f81f1405d35b66126a5baec6c8557587d907d6fc42ee8959</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19403940</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2872,17 +2864,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786133357</t>
+          <t>1786135338</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>7.677543</t>
+          <t>4.792453</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,7 +2891,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x1fcc69e05756a9495c54cf92ec95cc3fa98841963ff82dbc95bde1118d0e88d6</t>
+          <t>0xbdbdd9823b5c0238c109c0b23805ef0ff9a61aa34409f875e76398a0a7d6a460</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2907,31 +2899,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13.75169</t>
+          <t>48.04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2954,7 +2938,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2984,7 +2968,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786132692</t>
+          <t>1786135338</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2994,7 +2978,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>41.514536</t>
+          <t>181.283019</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3011,7 +2995,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x633e302e1f4a45e6cae190310048fc5640fdefddf9379c3100fb1c66a99ed226</t>
+          <t>0x6e5e8a0fc2f92f97555f424e1454c8c7768aee012cd36da5c6482cae7684c76a</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3019,23 +3003,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>855.42</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3043,27 +3035,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3088,17 +3080,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786129763</t>
+          <t>1786135337</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1555.309091</t>
+          <t>7.577358</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3115,7 +3107,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x0630cb5bb6cb2cff5cff3d307163d367059153070ce4cc710f35aa8d5c0c6825</t>
+          <t>0xe9b4cf790ad6491c958a9df98bf381066cbab97000c72aaa03df184df175418c</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3123,23 +3115,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>8.36113</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3147,27 +3147,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786129750</t>
+          <t>1786135296</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>132.545455</t>
+          <t>25.241147</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,31 +3219,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x7935024ab7987fd550aa17e789e9bdc95e2fbd51b52763713f00cf3fdfce8bdd</t>
+          <t>0xadbd273938f30f3bb961943289c77aa5d38f5773b41a5f47fdaa69aaae6f92c6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>14.33</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.6513</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3251,27 +3259,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x8a99a50823ade222f81f1405d35b66126a5baec6c8557587d907d6fc42ee8959</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3296,17 +3304,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786129738</t>
+          <t>1786133357</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>26.054545</t>
+          <t>7.677543</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3323,7 +3331,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x2b5a8f7ff44e3e83441016e9d07c7203d32fcbd029be82f693028e41ea14167e</t>
+          <t>0x1fcc69e05756a9495c54cf92ec95cc3fa98841963ff82dbc95bde1118d0e88d6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3331,23 +3339,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6.20999</t>
+          <t>13.75169</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3355,27 +3371,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3400,17 +3416,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786129725</t>
+          <t>1786132692</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>11.290891</t>
+          <t>41.514536</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3427,7 +3443,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x9be5cfaca91d026b377dc51c41481c7420f402caa117cd1a71bf175f81b8ba3f</t>
+          <t>0x633e302e1f4a45e6cae190310048fc5640fdefddf9379c3100fb1c66a99ed226</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3438,7 +3454,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>855.42</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3504,7 +3520,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786129713</t>
+          <t>1786129763</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3514,7 +3530,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>31.436364</t>
+          <t>1555.309091</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3531,7 +3547,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xffdb31c98c0c9e42bd2a3a4ac8c08c4dddf1bac9229455355ddf0f61eda11f5f</t>
+          <t>0x0630cb5bb6cb2cff5cff3d307163d367059153070ce4cc710f35aa8d5c0c6825</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3542,7 +3558,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>52.93</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3608,7 +3624,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786129699</t>
+          <t>1786129750</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3618,7 +3634,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>96.236364</t>
+          <t>132.545455</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3635,7 +3651,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x171c10e2c280f22ecd4a761a066bbcf7603ce72eb3464dbacf9b961ad202fb59</t>
+          <t>0x7935024ab7987fd550aa17e789e9bdc95e2fbd51b52763713f00cf3fdfce8bdd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3646,7 +3662,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>215.36</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3712,7 +3728,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786129686</t>
+          <t>1786129738</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3722,7 +3738,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>391.563636</t>
+          <t>26.054545</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3739,7 +3755,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x5ea684350a1a0b65d0f38be341db1516c1df4fe66d544944688193d0c3e3f0de</t>
+          <t>0x2b5a8f7ff44e3e83441016e9d07c7203d32fcbd029be82f693028e41ea14167e</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3747,19 +3763,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>495.02</t>
+          <t>6.20999</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3767,11 +3779,7 @@
           <t>Under/Over (4.5)</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3824,7 +3832,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786129356</t>
+          <t>1786129725</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3834,7 +3842,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>995.015075</t>
+          <t>11.290891</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3851,7 +3859,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x1a61ba580443c208fcf8a35afa56d0df4aaad017c49874a664c65a6551ec7d84</t>
+          <t>0x9be5cfaca91d026b377dc51c41481c7420f402caa117cd1a71bf175f81b8ba3f</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3859,19 +3867,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>495.02</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3879,11 +3883,7 @@
           <t>Under/Over (4.5)</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786129323</t>
+          <t>1786129713</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>995.015075</t>
+          <t>31.436364</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3963,7 +3963,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xbc4a52ef8f6d90db800339bd0fdc45e1e4887cc29721741fa364564427cebc93</t>
+          <t>0xffdb31c98c0c9e42bd2a3a4ac8c08c4dddf1bac9229455355ddf0f61eda11f5f</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3971,19 +3971,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>52.93</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3991,11 +3987,7 @@
           <t>Under/Over (4.5)</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4048,7 +4040,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786129297</t>
+          <t>1786129699</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4058,7 +4050,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>97.507538</t>
+          <t>96.236364</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4075,7 +4067,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x009e27d36e3bfb01593b611eb8138842f7baf97d375a4302c10337f4fa65da7a</t>
+          <t>0x171c10e2c280f22ecd4a761a066bbcf7603ce72eb3464dbacf9b961ad202fb59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4083,19 +4075,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>215.36</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4103,11 +4091,7 @@
           <t>Under/Over (4.5)</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4160,7 +4144,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786128259</t>
+          <t>1786129686</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4170,7 +4154,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>152.897196</t>
+          <t>391.563636</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4187,7 +4171,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x987370b50d0502b7fd566ef6bb2bf38112c25bf81110ad0b1926b02ffd8ccd9d</t>
+          <t>0x5ea684350a1a0b65d0f38be341db1516c1df4fe66d544944688193d0c3e3f0de</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4202,22 +4186,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>495.02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -3</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4227,27 +4211,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4272,17 +4256,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786127657</t>
+          <t>1786129356</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>5.94717</t>
+          <t>995.015075</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4299,7 +4283,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x38207556aceeaaa6ba9394fe5b398b808e1d67e0bba9c3b0fa61a88d5c5aebb7</t>
+          <t>0x1a61ba580443c208fcf8a35afa56d0df4aaad017c49874a664c65a6551ec7d84</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4314,22 +4298,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21.40562</t>
+          <t>495.02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.0737</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4339,27 +4323,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4384,17 +4368,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786126212</t>
+          <t>1786129323</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>290.245695</t>
+          <t>995.015075</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4411,7 +4395,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x83a78ff6339d485633ea010240dad1c0ad7f4a30a2628cd7eb01ab0370275ddc</t>
+          <t>0xbc4a52ef8f6d90db800339bd0fdc45e1e4887cc29721741fa364564427cebc93</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4419,23 +4403,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.76023</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4458,7 +4450,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4488,7 +4480,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786125622</t>
+          <t>1786129297</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4498,7 +4490,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>10.292389</t>
+          <t>97.507538</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4515,36 +4507,44 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x5630ba52ae08208c16f996b3fc5f0ab29f63363f75b764a890d5196f1a24e9b9</t>
+          <t>0x009e27d36e3bfb01593b611eb8138842f7baf97d375a4302c10337f4fa65da7a</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x6e70489F443F69f1a091af8509f0b99338460D39</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>249.99999</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786125585</t>
+          <t>1786128259</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>469.483549</t>
+          <t>152.897196</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4619,59 +4619,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x272659eb9c2a40b218a61bdb98731190ae92104b09c8c08096e7cacce4e2dc79</t>
+          <t>0x987370b50d0502b7fd566ef6bb2bf38112c25bf81110ad0b1926b02ffd8ccd9d</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4696,17 +4704,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786125525</t>
+          <t>1786127657</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>9.389671</t>
+          <t>5.94717</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4723,59 +4731,67 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xc8538d15c53a4c377da962db1d0193aab217862d8ad9ac90a3999b587e2a1c53</t>
+          <t>0x38207556aceeaaa6ba9394fe5b398b808e1d67e0bba9c3b0fa61a88d5c5aebb7</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>76.29599</t>
+          <t>21.40562</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5312</t>
+          <t>1.0737</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4800,17 +4816,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786125507</t>
+          <t>1786126212</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>143.615981</t>
+          <t>290.245695</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4827,7 +4843,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xcb1bccb079df818106a903bda81def1d78bea048113133314cb9b5de80505b9a</t>
+          <t>0x83a78ff6339d485633ea010240dad1c0ad7f4a30a2628cd7eb01ab0370275ddc</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4835,54 +4851,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.14001</t>
+          <t>4.76023</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4912,7 +4920,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786124259</t>
+          <t>1786125622</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4922,7 +4930,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>10.894763</t>
+          <t>10.292389</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4939,62 +4947,54 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x7b5620344652130ca3f87e52b00289e9ee38aab6c426c0e9cd693b417361526c</t>
+          <t>0x5630ba52ae08208c16f996b3fc5f0ab29f63363f75b764a890d5196f1a24e9b9</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x6e70489F443F69f1a091af8509f0b99338460D39</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>249.99999</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786124259</t>
+          <t>1786125585</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>157.894737</t>
+          <t>469.483549</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,62 +5051,54 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xdc6c27f0359af82e276a61c449bef19ee4c2778a601eecfac8b0ae278c4fed31</t>
+          <t>0x272659eb9c2a40b218a61bdb98731190ae92104b09c8c08096e7cacce4e2dc79</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.3787</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5136,7 +5128,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786124228</t>
+          <t>1786125525</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5146,7 +5138,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>168.844884</t>
+          <t>9.389671</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5163,62 +5155,54 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xb740a9883984f2d057b5bd144c80df89d3be4972b6802619769be156582f7530</t>
+          <t>0xc8538d15c53a4c377da962db1d0193aab217862d8ad9ac90a3999b587e2a1c53</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>56.08</t>
+          <t>76.29599</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.3725</t>
+          <t>1.5312</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5248,7 +5232,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786123222</t>
+          <t>1786125507</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5258,7 +5242,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>150.550336</t>
+          <t>143.615981</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5275,12 +5259,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x1eb675eb4dddff6e46c7fe87ea19a03c7d5274c16759609d8d9cad3c46312d55</t>
+          <t>0xcb1bccb079df818106a903bda81def1d78bea048113133314cb9b5de80505b9a</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5290,12 +5274,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.14001</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5305,7 +5289,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5330,7 +5314,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5360,7 +5344,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786123213</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5370,7 +5354,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>14.349776</t>
+          <t>10.894763</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5387,23 +5371,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
+          <t>0x7b5620344652130ca3f87e52b00289e9ee38aab6c426c0e9cd693b417361526c</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5411,7 +5399,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5434,7 +5426,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5464,7 +5456,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786122007</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5474,7 +5466,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13.62862</t>
+          <t>157.894737</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5491,31 +5483,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
+          <t>0xdc6c27f0359af82e276a61c449bef19ee4c2778a601eecfac8b0ae278c4fed31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4563</t>
+          <t>1.3787</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786117951</t>
+          <t>1786124228</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>43.769863</t>
+          <t>168.844884</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5595,31 +5595,39 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
+          <t>0xb740a9883984f2d057b5bd144c80df89d3be4972b6802619769be156582f7530</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>56.08</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.6812</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5642,7 +5650,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5672,7 +5680,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786116835</t>
+          <t>1786123222</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5682,7 +5690,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1.467861</t>
+          <t>150.550336</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5699,23 +5707,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
+          <t>0x1eb675eb4dddff6e46c7fe87ea19a03c7d5274c16759609d8d9cad3c46312d55</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5723,7 +5735,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5731,27 +5747,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5776,17 +5792,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786115830</t>
+          <t>1786123213</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>14.349776</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5803,23 +5819,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
+          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.36999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5835,27 +5851,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5880,17 +5896,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786115829</t>
+          <t>1786122007</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1.985493</t>
+          <t>13.62862</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5907,28 +5923,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
+          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.4563</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5939,27 +5955,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5984,17 +6000,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786115827</t>
+          <t>1786117951</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1.463754</t>
+          <t>43.769863</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6011,62 +6027,54 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
+          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.6812</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6096,7 +6104,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786115129</t>
+          <t>1786116835</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6106,7 +6114,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>13.559322</t>
+          <t>1.467861</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6123,28 +6131,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
+          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6155,27 +6163,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6200,17 +6208,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786115128</t>
+          <t>1786115830</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>9.852217</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6227,27 +6235,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
+          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>1.36999</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6255,11 +6259,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6267,27 +6267,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6312,17 +6312,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786115829</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>85.387755</t>
+          <t>1.985493</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6339,28 +6339,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
+          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>177.44126</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -6371,27 +6371,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786115827</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>350.501254</t>
+          <t>1.463754</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6443,12 +6443,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
+          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6483,27 +6483,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6528,17 +6528,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786111515</t>
+          <t>1786115129</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1.698514</t>
+          <t>13.559322</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6555,39 +6555,31 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
+          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.5075</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6595,27 +6587,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6640,17 +6632,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786105696</t>
+          <t>1786115128</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>16.985121</t>
+          <t>9.852217</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6667,12 +6659,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
+          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6682,22 +6674,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4.49993</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.9463</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6707,7 +6699,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6717,12 +6709,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6752,7 +6744,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786104752</t>
+          <t>1786115115</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6762,7 +6754,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>4.75554</t>
+          <t>85.387755</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6779,39 +6771,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
+          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5.99989</t>
+          <t>177.44126</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Over 0.5</t>
-        </is>
-      </c>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6819,7 +6803,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6829,12 +6813,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6864,7 +6848,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786104743</t>
+          <t>1786115115</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6874,7 +6858,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>6.34909</t>
+          <t>350.501254</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6891,31 +6875,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6923,27 +6915,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6968,17 +6960,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786102413</t>
+          <t>1786111515</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>3.706122</t>
+          <t>1.698514</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6995,31 +6987,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.2212</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7027,27 +7027,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786102412</t>
+          <t>1786105696</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>4.519774</t>
+          <t>16.985121</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7099,31 +7099,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.49993</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.9463</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7131,27 +7139,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7176,17 +7184,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786102410</t>
+          <t>1786104752</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>2.416918</t>
+          <t>4.75554</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7203,31 +7211,39 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5.99989</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.945</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7235,27 +7251,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7280,17 +7296,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786102409</t>
+          <t>1786104743</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>5.128205</t>
+          <t>6.34909</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7307,39 +7323,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7347,27 +7355,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7392,17 +7400,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786096483</t>
+          <t>1786102413</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>151.554007</t>
+          <t>3.706122</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7419,39 +7427,31 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.2212</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7459,27 +7459,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7504,17 +7504,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786095316</t>
+          <t>1786102412</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>15.69338</t>
+          <t>4.519774</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7531,27 +7531,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7559,11 +7555,7 @@
           <t>Under/Over (3.5)</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7571,27 +7563,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7616,17 +7608,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786086947</t>
+          <t>1786102410</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>503.272727</t>
+          <t>2.416918</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7643,39 +7635,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20.39624</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7683,27 +7667,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7728,17 +7712,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786082661</t>
+          <t>1786102409</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>54.389973</t>
+          <t>5.128205</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7755,31 +7739,39 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>54.37</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.3588</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7787,27 +7779,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7832,17 +7824,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786096483</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>151.554007</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7859,31 +7851,39 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.3588</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786095316</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>15.69338</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7963,110 +7963,542 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1786086947</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>503.272727</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>20.39624</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.375</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1786082661</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>54.389973</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>14.19</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.5675</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1786076493</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>25.004405</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="V75" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V75"/>
+  <dimension ref="A1:V81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xe8ac9d951a75bfb5f85a9df2129b2402e3d7896e9994d96820f9c2abd9dfd94c</t>
+          <t>0x690d059036b093e4b5b7c5348dcaf6e9c0038ffbd846a8822dfacb478490df81</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.59894</t>
+          <t>22.594</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.6875</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NEC Nijmegen -2</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs SC Telstar</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x1ad454c96c47b60c3469ca957e70ba1e03d07a5415f5e1d36eb27c71b1b71929</t>
+          <t>0x4882e1214422a29af689a209790d0484e91067d78c514ab50b9376875ef6c6da</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19403940</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786162832</t>
+          <t>1786172307</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>29.148949</t>
+          <t>32.864</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xc2ff6b7ef5c4d6b1ae7fb27264146c018690220314bfbd5d9f754aed33050ad1</t>
+          <t>0x515f932c5d84342ff2016d68164d65c1b5e6c186e6404727ea74c0d2b65ce561</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,23 +651,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>4.67862</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.1787</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar -2</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
+          <t>0xf88c6c4c9ed7484ff9bb259e779c42b8d62be41b33e50dbe39ff05ae3c3ced3d</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786161973</t>
+          <t>1786172307</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>9.846154</t>
+          <t>14.678024</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x75f10c8c3b07bcf97178db485e61f1e964f7925053c699f8e7ae25fdef0517ba</t>
+          <t>0x56584057b73ca4fdc229b61705b847a20afe82ac4a0c60c32239241b70855884</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,12 +770,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.1125</t>
+          <t>1.8313</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -777,7 +785,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x2fbec757a98798a9e344fdcfeba32267077a6f189c5785b7b423a7d4efc507cd</t>
+          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786161973</t>
+          <t>1786171005</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>35.288889</t>
+          <t>6.015002</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xe31905b26a7e1536bf125b184f1294f656fa4f22b6e9fd739a0a032c4d321ce0</t>
+          <t>0x4988973efa2319ec17ed8f106880149d2870b9a4d2d1289bda5ef17eb6394876</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -870,17 +878,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9.73576</t>
+          <t>3.83583</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1787</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -906,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
+          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786161913</t>
+          <t>1786170645</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>54.46579</t>
+          <t>18.265857</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xb3bc0ed4c483bee8be05ae8fc496bbe64b2b2dad9597773c67ca17df236c46c6</t>
+          <t>0x1c5485873f863e5524d43f85a405dd076d4f362bfdb51537d55265f9b03bdfc3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -971,31 +979,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786158954</t>
+          <t>1786170645</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>10.094545</t>
+          <t>19.439614</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,7 +1075,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x73f8172d3365445d5d6481e5b681390927b19eba83d829e34347ddf969f4d3aa</t>
+          <t>0x8313f084f33c053a91835e9b9fa41d85e94dc7e2791909d44626fbdaafcc978c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1083,23 +1083,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.3088</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar -2</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1107,27 +1115,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x70ad3839eaf0acb3b01efaf7fbad4dc4e6d59e9cba36c93a59ba571f812853a5</t>
+          <t>0xf88c6c4c9ed7484ff9bb259e779c42b8d62be41b33e50dbe39ff05ae3c3ced3d</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786158954</t>
+          <t>1786165678</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>14.486486</t>
+          <t>17.619433</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,31 +1187,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x49223560553949c798e427bb609beb8d54b408bb92fac667c5e805a35d272dd8</t>
+          <t>0xe8ac9d951a75bfb5f85a9df2129b2402e3d7896e9994d96820f9c2abd9dfd94c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.59894</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen -2</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1211,27 +1227,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x9a0bc510c3953793967123d2592a887e55b2c7b4d336100e6a3528497b495765</t>
+          <t>0x1ad454c96c47b60c3469ca957e70ba1e03d07a5415f5e1d36eb27c71b1b71929</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1256,17 +1272,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786158687</t>
+          <t>1786162832</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.687764</t>
+          <t>29.148949</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,28 +1299,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x52a28d048aabdc20f81aa23618c25399119d945b7c7afae212c263d469fce473</t>
+          <t>0xc2ff6b7ef5c4d6b1ae7fb27264146c018690220314bfbd5d9f754aed33050ad1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.1787</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1330,7 +1346,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1360,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786158626</t>
+          <t>1786161973</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1370,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.439024</t>
+          <t>9.846154</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,12 +1403,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x654ee8bcaf6b781089890f7528b8d264645cbb382b68a3166b49f74e9e50d5fa</t>
+          <t>0x75f10c8c3b07bcf97178db485e61f1e964f7925053c699f8e7ae25fdef0517ba</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1402,22 +1418,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.1125</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1427,27 +1443,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x700c0930687f6c1dc816f7af554f65cf4b2844ee77830f992d4a731c0df2564f</t>
+          <t>0x2fbec757a98798a9e344fdcfeba32267077a6f189c5785b7b423a7d4efc507cd</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1472,17 +1488,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786158491</t>
+          <t>1786161973</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.033592</t>
+          <t>35.288889</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,39 +1515,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x38b906d6e5d0de2738537770dc05e6338898a8b937e89cbc914ae6e75513308b</t>
+          <t>0xe31905b26a7e1536bf125b184f1294f656fa4f22b6e9fd739a0a032c4d321ce0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>9.73576</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.1787</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1539,27 +1547,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x2ea149fa9b38b9090f5b506ae3dca75e0788add16a579f9705e6feb502e84868</t>
+          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1584,17 +1592,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786158491</t>
+          <t>1786161913</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.033592</t>
+          <t>54.46579</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,31 +1619,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x598f4044b8d7101954a12cfb6a028285705b009e647d167cb12be8cc1aa8c433</t>
+          <t>0xb3bc0ed4c483bee8be05ae8fc496bbe64b2b2dad9597773c67ca17df236c46c6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1643,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs SC Telstar</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x9455b4a5e4ea76ab5db55d0b29615eeae7a6c51e3bc31b5c6b0ed2395a188551</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19403940</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1688,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786158381</t>
+          <t>1786158954</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.781719</t>
+          <t>10.094545</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,28 +1731,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x7eaedb8f4752259366867abf771d84c0d99e47010227fd51681abeb60b48411b</t>
+          <t>0x73f8172d3365445d5d6481e5b681390927b19eba83d829e34347ddf969f4d3aa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.1638</t>
+          <t>1.0925</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1747,27 +1763,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xc998a4ccb6265ea2336288383810c1b769d49949dbefbe46fcd473372116b82c</t>
+          <t>0x70ad3839eaf0acb3b01efaf7fbad4dc4e6d59e9cba36c93a59ba571f812853a5</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1792,17 +1808,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786146812</t>
+          <t>1786158954</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>6.10687</t>
+          <t>14.486486</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,12 +1835,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xc17004473d1c14453448f29404ac7988d663c0f1eac3d80503d006f04db8d7a6</t>
+          <t>0x49223560553949c798e427bb609beb8d54b408bb92fac667c5e805a35d272dd8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1835,12 +1851,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3725</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1866,7 +1882,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x836ea569e8bb4a65752149e8c476f1184a85ddb5570c5106624ba137f9a0a2d5</t>
+          <t>0x9a0bc510c3953793967123d2592a887e55b2c7b4d336100e6a3528497b495765</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1912,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786146806</t>
+          <t>1786158687</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1922,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2.684564</t>
+          <t>1.687764</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,12 +1939,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x88de27964fdb5afcbdf9d01c80c57e6ae6197056927b86aeb5d5e9260acc2828</t>
+          <t>0x52a28d048aabdc20f81aa23618c25399119d945b7c7afae212c263d469fce473</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1939,12 +1955,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.0775</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1955,27 +1971,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xca6f32a50927cbde2cb395d95e723ecf21a4b1811b744369dad7d460f821dd6d</t>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2000,17 +2016,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786146805</t>
+          <t>1786158626</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>12.903226</t>
+          <t>2.439024</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,31 +2043,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x7c22fadfd0e1f902b93e750db5984c247214d30b4fe99214ef93a9e2ad497877</t>
+          <t>0x654ee8bcaf6b781089890f7528b8d264645cbb382b68a3166b49f74e9e50d5fa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.1625</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2059,27 +2083,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PEC Zwolle vs Ajax Amsterdam</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xdd44346ee5e92ddeb574c7b372f2f6e8cfcd74de2a5309e9003a1550bcc12ab0</t>
+          <t>0x700c0930687f6c1dc816f7af554f65cf4b2844ee77830f992d4a731c0df2564f</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19403941</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2104,17 +2128,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786146805</t>
+          <t>1786158491</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>6.153846</t>
+          <t>1.033592</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2131,12 +2155,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xb38a3cc2cf9c03f99487ec03657f937b47155f02bc75d79ffc33db76f98a69a6</t>
+          <t>0x38b906d6e5d0de2738537770dc05e6338898a8b937e89cbc914ae6e75513308b</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2146,22 +2170,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.52135</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -3</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2171,27 +2195,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0x2ea149fa9b38b9090f5b506ae3dca75e0788add16a579f9705e6feb502e84868</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2216,17 +2240,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786142904</t>
+          <t>1786158491</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>34.011365</t>
+          <t>1.033592</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2243,39 +2267,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x7a20466d35539c024b1d077354a8e89cf90472d7db1127f1ec7682095c931015</t>
+          <t>0x598f4044b8d7101954a12cfb6a028285705b009e647d167cb12be8cc1aa8c433</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9.70945</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2283,27 +2299,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0x9455b4a5e4ea76ab5db55d0b29615eeae7a6c51e3bc31b5c6b0ed2395a188551</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2328,17 +2344,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786142904</t>
+          <t>1786158381</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>21.339451</t>
+          <t>1.781719</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2355,39 +2371,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x3e2fa39473c09803be951522f0cce2a88e71007867e0d6a0ae033e851124bc38</t>
+          <t>0x7eaedb8f4752259366867abf771d84c0d99e47010227fd51681abeb60b48411b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>367.52999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.1638</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2395,27 +2403,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0xc998a4ccb6265ea2336288383810c1b769d49949dbefbe46fcd473372116b82c</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2440,17 +2448,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786142696</t>
+          <t>1786146812</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>624.25476</t>
+          <t>6.10687</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,28 +2475,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xd9c75ae7cbf7ebba9529c5699532d10d62802be6aac9ffc45052aa92cc35d72d</t>
+          <t>0xc17004473d1c14453448f29404ac7988d663c0f1eac3d80503d006f04db8d7a6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2514,7 +2522,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x4882e1214422a29af689a209790d0484e91067d78c514ab50b9376875ef6c6da</t>
+          <t>0x836ea569e8bb4a65752149e8c476f1184a85ddb5570c5106624ba137f9a0a2d5</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2544,7 +2552,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786142027</t>
+          <t>1786146806</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2554,7 +2562,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>50.64684</t>
+          <t>2.684564</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,39 +2579,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x417760c1d35fd131f695db2c7f2e8400a5d3d5d5903b79ac1ca222a5a30d0134</t>
+          <t>0x88de27964fdb5afcbdf9d01c80c57e6ae6197056927b86aeb5d5e9260acc2828</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.0775</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -2</t>
-        </is>
-      </c>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2611,27 +2611,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xd9978e221ac5eb1139faeeefdedfd12ffe6f1986a602f6669e76abce9bb9067d</t>
+          <t>0xca6f32a50927cbde2cb395d95e723ecf21a4b1811b744369dad7d460f821dd6d</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786140016</t>
+          <t>1786146805</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2.101545</t>
+          <t>12.903226</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,28 +2683,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x16fd77e28d16ec069fe859b1ad63a1ce956b06b6136d6ac68ccdb02be6b3c94c</t>
+          <t>0x7c22fadfd0e1f902b93e750db5984c247214d30b4fe99214ef93a9e2ad497877</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.8475</t>
+          <t>1.1625</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2715,27 +2715,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs SC Telstar</t>
+          <t>PEC Zwolle vs Ajax Amsterdam</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>Ajax Amsterdam</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x656b05c8c9e0a63d26fa6dcc4ddf398d649bc013ac423819523cf94211567658</t>
+          <t>0xdd44346ee5e92ddeb574c7b372f2f6e8cfcd74de2a5309e9003a1550bcc12ab0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19403940</t>
+          <t>L19403941</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786136525</t>
+          <t>1786146805</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>11.79941</t>
+          <t>6.153846</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,7 +2787,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xd3c8bb8d02330d8124e995d21959103edcd0baaa6289b159970a2225912e418d</t>
+          <t>0xb38a3cc2cf9c03f99487ec03657f937b47155f02bc75d79ffc33db76f98a69a6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2795,23 +2795,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>11.52135</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2834,7 +2842,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2864,7 +2872,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786135338</t>
+          <t>1786142904</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2874,7 +2882,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>4.792453</t>
+          <t>34.011365</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,7 +2899,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xbdbdd9823b5c0238c109c0b23805ef0ff9a61aa34409f875e76398a0a7d6a460</t>
+          <t>0x7a20466d35539c024b1d077354a8e89cf90472d7db1127f1ec7682095c931015</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2899,23 +2907,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>9.70945</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -2.5</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2938,7 +2954,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2968,7 +2984,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786135338</t>
+          <t>1786142904</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2978,7 +2994,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>181.283019</t>
+          <t>21.339451</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2995,12 +3011,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x6e5e8a0fc2f92f97555f424e1454c8c7768aee012cd36da5c6482cae7684c76a</t>
+          <t>0x3e2fa39473c09803be951522f0cce2a88e71007867e0d6a0ae033e851124bc38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3010,22 +3026,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>367.52999</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -3</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3035,27 +3051,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3080,17 +3096,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786135337</t>
+          <t>1786142696</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>7.577358</t>
+          <t>624.25476</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,39 +3123,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xe9b4cf790ad6491c958a9df98bf381066cbab97000c72aaa03df184df175418c</t>
+          <t>0xd9c75ae7cbf7ebba9529c5699532d10d62802be6aac9ffc45052aa92cc35d72d</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.36113</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3147,27 +3155,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0x4882e1214422a29af689a209790d0484e91067d78c514ab50b9376875ef6c6da</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3192,17 +3200,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786135296</t>
+          <t>1786142027</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>25.241147</t>
+          <t>50.64684</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,12 +3227,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xadbd273938f30f3bb961943289c77aa5d38f5773b41a5f47fdaa69aaae6f92c6</t>
+          <t>0x417760c1d35fd131f695db2c7f2e8400a5d3d5d5903b79ac1ca222a5a30d0134</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3234,22 +3242,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.6513</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>PSV Eindhoven -2</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3259,27 +3267,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs SC Telstar</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x8a99a50823ade222f81f1405d35b66126a5baec6c8557587d907d6fc42ee8959</t>
+          <t>0xd9978e221ac5eb1139faeeefdedfd12ffe6f1986a602f6669e76abce9bb9067d</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19403940</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3304,17 +3312,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786133357</t>
+          <t>1786140016</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>7.677543</t>
+          <t>2.101545</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3331,7 +3339,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x1fcc69e05756a9495c54cf92ec95cc3fa98841963ff82dbc95bde1118d0e88d6</t>
+          <t>0x16fd77e28d16ec069fe859b1ad63a1ce956b06b6136d6ac68ccdb02be6b3c94c</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3339,31 +3347,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>13.75169</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.8475</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3371,27 +3371,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0x656b05c8c9e0a63d26fa6dcc4ddf398d649bc013ac423819523cf94211567658</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786132692</t>
+          <t>1786136525</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>41.514536</t>
+          <t>11.79941</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x633e302e1f4a45e6cae190310048fc5640fdefddf9379c3100fb1c66a99ed226</t>
+          <t>0xd3c8bb8d02330d8124e995d21959103edcd0baaa6289b159970a2225912e418d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3454,17 +3454,17 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>855.42</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3475,27 +3475,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3520,17 +3520,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786129763</t>
+          <t>1786135338</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1555.309091</t>
+          <t>4.792453</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3547,7 +3547,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x0630cb5bb6cb2cff5cff3d307163d367059153070ce4cc710f35aa8d5c0c6825</t>
+          <t>0xbdbdd9823b5c0238c109c0b23805ef0ff9a61aa34409f875e76398a0a7d6a460</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3558,17 +3558,17 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>48.04</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3579,27 +3579,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3624,17 +3624,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786129750</t>
+          <t>1786135338</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>132.545455</t>
+          <t>181.283019</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3651,7 +3651,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x7935024ab7987fd550aa17e789e9bdc95e2fbd51b52763713f00cf3fdfce8bdd</t>
+          <t>0x6e5e8a0fc2f92f97555f424e1454c8c7768aee012cd36da5c6482cae7684c76a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3659,23 +3659,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>14.33</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3683,27 +3691,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3728,17 +3736,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786129738</t>
+          <t>1786135337</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>26.054545</t>
+          <t>7.577358</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3755,7 +3763,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x2b5a8f7ff44e3e83441016e9d07c7203d32fcbd029be82f693028e41ea14167e</t>
+          <t>0xe9b4cf790ad6491c958a9df98bf381066cbab97000c72aaa03df184df175418c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3763,23 +3771,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6.20999</t>
+          <t>8.36113</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3787,27 +3803,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3832,17 +3848,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786129725</t>
+          <t>1786135296</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>11.290891</t>
+          <t>25.241147</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3859,31 +3875,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x9be5cfaca91d026b377dc51c41481c7420f402caa117cd1a71bf175f81b8ba3f</t>
+          <t>0xadbd273938f30f3bb961943289c77aa5d38f5773b41a5f47fdaa69aaae6f92c6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.6513</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3891,27 +3915,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x8a99a50823ade222f81f1405d35b66126a5baec6c8557587d907d6fc42ee8959</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3936,17 +3960,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786129713</t>
+          <t>1786133357</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>31.436364</t>
+          <t>7.677543</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3963,7 +3987,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xffdb31c98c0c9e42bd2a3a4ac8c08c4dddf1bac9229455355ddf0f61eda11f5f</t>
+          <t>0x1fcc69e05756a9495c54cf92ec95cc3fa98841963ff82dbc95bde1118d0e88d6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3971,23 +3995,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>52.93</t>
+          <t>13.75169</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3995,27 +4027,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4040,17 +4072,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786129699</t>
+          <t>1786132692</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>96.236364</t>
+          <t>41.514536</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4067,7 +4099,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x171c10e2c280f22ecd4a761a066bbcf7603ce72eb3464dbacf9b961ad202fb59</t>
+          <t>0x633e302e1f4a45e6cae190310048fc5640fdefddf9379c3100fb1c66a99ed226</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4078,7 +4110,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>215.36</t>
+          <t>855.42</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4144,7 +4176,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786129686</t>
+          <t>1786129763</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4154,7 +4186,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>391.563636</t>
+          <t>1555.309091</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,7 +4203,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x5ea684350a1a0b65d0f38be341db1516c1df4fe66d544944688193d0c3e3f0de</t>
+          <t>0x0630cb5bb6cb2cff5cff3d307163d367059153070ce4cc710f35aa8d5c0c6825</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4179,19 +4211,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>495.02</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4199,11 +4227,7 @@
           <t>Under/Over (4.5)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4256,7 +4280,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786129356</t>
+          <t>1786129750</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4266,7 +4290,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>995.015075</t>
+          <t>132.545455</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4283,7 +4307,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x1a61ba580443c208fcf8a35afa56d0df4aaad017c49874a664c65a6551ec7d84</t>
+          <t>0x7935024ab7987fd550aa17e789e9bdc95e2fbd51b52763713f00cf3fdfce8bdd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4291,19 +4315,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>495.02</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4311,11 +4331,7 @@
           <t>Under/Over (4.5)</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4368,7 +4384,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786129323</t>
+          <t>1786129738</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4378,7 +4394,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>995.015075</t>
+          <t>26.054545</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4395,7 +4411,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xbc4a52ef8f6d90db800339bd0fdc45e1e4887cc29721741fa364564427cebc93</t>
+          <t>0x2b5a8f7ff44e3e83441016e9d07c7203d32fcbd029be82f693028e41ea14167e</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4403,19 +4419,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>6.20999</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4423,11 +4435,7 @@
           <t>Under/Over (4.5)</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4480,7 +4488,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786129297</t>
+          <t>1786129725</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4490,7 +4498,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>97.507538</t>
+          <t>11.290891</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4507,7 +4515,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x009e27d36e3bfb01593b611eb8138842f7baf97d375a4302c10337f4fa65da7a</t>
+          <t>0x9be5cfaca91d026b377dc51c41481c7420f402caa117cd1a71bf175f81b8ba3f</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4515,19 +4523,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4535,11 +4539,7 @@
           <t>Under/Over (4.5)</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786128259</t>
+          <t>1786129713</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>152.897196</t>
+          <t>31.436364</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4619,7 +4619,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x987370b50d0502b7fd566ef6bb2bf38112c25bf81110ad0b1926b02ffd8ccd9d</t>
+          <t>0xffdb31c98c0c9e42bd2a3a4ac8c08c4dddf1bac9229455355ddf0f61eda11f5f</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4627,31 +4627,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>52.93</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4659,27 +4651,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4704,17 +4696,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786127657</t>
+          <t>1786129699</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>5.94717</t>
+          <t>96.236364</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,7 +4723,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x38207556aceeaaa6ba9394fe5b398b808e1d67e0bba9c3b0fa61a88d5c5aebb7</t>
+          <t>0x171c10e2c280f22ecd4a761a066bbcf7603ce72eb3464dbacf9b961ad202fb59</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4739,31 +4731,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>21.40562</t>
+          <t>215.36</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.0737</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Fortuna Sittard</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4771,27 +4755,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4816,17 +4800,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786126212</t>
+          <t>1786129686</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>290.245695</t>
+          <t>391.563636</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4843,7 +4827,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x83a78ff6339d485633ea010240dad1c0ad7f4a30a2628cd7eb01ab0370275ddc</t>
+          <t>0x5ea684350a1a0b65d0f38be341db1516c1df4fe66d544944688193d0c3e3f0de</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4851,23 +4835,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.76023</t>
+          <t>495.02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4890,7 +4882,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4920,7 +4912,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786125622</t>
+          <t>1786129356</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4930,7 +4922,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>10.292389</t>
+          <t>995.015075</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,36 +4939,44 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x5630ba52ae08208c16f996b3fc5f0ab29f63363f75b764a890d5196f1a24e9b9</t>
+          <t>0x1a61ba580443c208fcf8a35afa56d0df4aaad017c49874a664c65a6551ec7d84</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x6e70489F443F69f1a091af8509f0b99338460D39</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>249.99999</t>
+          <t>495.02</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786125585</t>
+          <t>1786129323</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>469.483549</t>
+          <t>995.015075</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,36 +5051,44 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x272659eb9c2a40b218a61bdb98731190ae92104b09c8c08096e7cacce4e2dc79</t>
+          <t>0xbc4a52ef8f6d90db800339bd0fdc45e1e4887cc29721741fa364564427cebc93</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -5098,7 +5106,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5128,7 +5136,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786125525</t>
+          <t>1786129297</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5138,7 +5146,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>9.389671</t>
+          <t>97.507538</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5155,36 +5163,44 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xc8538d15c53a4c377da962db1d0193aab217862d8ad9ac90a3999b587e2a1c53</t>
+          <t>0x009e27d36e3bfb01593b611eb8138842f7baf97d375a4302c10337f4fa65da7a</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>76.29599</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5312</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -5202,7 +5218,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5232,7 +5248,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786125507</t>
+          <t>1786128259</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5242,7 +5258,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>143.615981</t>
+          <t>152.897196</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5259,7 +5275,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xcb1bccb079df818106a903bda81def1d78bea048113133314cb9b5de80505b9a</t>
+          <t>0x987370b50d0502b7fd566ef6bb2bf38112c25bf81110ad0b1926b02ffd8ccd9d</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5274,22 +5290,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4.14001</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven -3</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5299,27 +5315,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5344,17 +5360,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786124259</t>
+          <t>1786127657</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>10.894763</t>
+          <t>5.94717</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5371,7 +5387,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x7b5620344652130ca3f87e52b00289e9ee38aab6c426c0e9cd693b417361526c</t>
+          <t>0x38207556aceeaaa6ba9394fe5b398b808e1d67e0bba9c3b0fa61a88d5c5aebb7</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5386,12 +5402,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>21.40562</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.0737</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5401,7 +5417,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5411,27 +5427,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5456,17 +5472,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786124259</t>
+          <t>1786126212</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>157.894737</t>
+          <t>290.245695</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5483,7 +5499,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xdc6c27f0359af82e276a61c449bef19ee4c2778a601eecfac8b0ae278c4fed31</t>
+          <t>0x83a78ff6339d485633ea010240dad1c0ad7f4a30a2628cd7eb01ab0370275ddc</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5491,54 +5507,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>4.76023</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3787</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5568,7 +5576,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786124228</t>
+          <t>1786125622</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5578,7 +5586,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>168.844884</t>
+          <t>10.292389</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5595,62 +5603,54 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xb740a9883984f2d057b5bd144c80df89d3be4972b6802619769be156582f7530</t>
+          <t>0x5630ba52ae08208c16f996b3fc5f0ab29f63363f75b764a890d5196f1a24e9b9</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x6e70489F443F69f1a091af8509f0b99338460D39</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>56.08</t>
+          <t>249.99999</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.3725</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786123222</t>
+          <t>1786125585</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>150.550336</t>
+          <t>469.483549</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5707,39 +5707,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x1eb675eb4dddff6e46c7fe87ea19a03c7d5274c16759609d8d9cad3c46312d55</t>
+          <t>0x272659eb9c2a40b218a61bdb98731190ae92104b09c8c08096e7cacce4e2dc79</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5762,7 +5754,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5792,7 +5784,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786123213</t>
+          <t>1786125525</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5802,7 +5794,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>14.349776</t>
+          <t>9.389671</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5819,28 +5811,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
+          <t>0xc8538d15c53a4c377da962db1d0193aab217862d8ad9ac90a3999b587e2a1c53</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>76.29599</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.5312</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5866,7 +5858,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5896,7 +5888,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786122007</t>
+          <t>1786125507</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5906,7 +5898,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>13.62862</t>
+          <t>143.615981</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5923,31 +5915,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
+          <t>0xcb1bccb079df818106a903bda81def1d78bea048113133314cb9b5de80505b9a</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>4.14001</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4563</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786117951</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>43.769863</t>
+          <t>10.894763</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6027,31 +6027,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
+          <t>0x7b5620344652130ca3f87e52b00289e9ee38aab6c426c0e9cd693b417361526c</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.6812</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6074,7 +6082,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6104,7 +6112,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786116835</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6114,7 +6122,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1.467861</t>
+          <t>157.894737</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6131,23 +6139,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
+          <t>0xdc6c27f0359af82e276a61c449bef19ee4c2778a601eecfac8b0ae278c4fed31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.3787</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6155,7 +6167,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6163,27 +6179,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6208,17 +6224,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786115830</t>
+          <t>1786124228</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>168.844884</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6235,23 +6251,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
+          <t>0xb740a9883984f2d057b5bd144c80df89d3be4972b6802619769be156582f7530</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.36999</t>
+          <t>56.08</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6259,7 +6279,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6267,27 +6291,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6312,17 +6336,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786115829</t>
+          <t>1786123222</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1.985493</t>
+          <t>150.550336</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6339,23 +6363,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
+          <t>0x1eb675eb4dddff6e46c7fe87ea19a03c7d5274c16759609d8d9cad3c46312d55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6363,7 +6391,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6371,27 +6403,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6416,17 +6448,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786115827</t>
+          <t>1786123213</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1.463754</t>
+          <t>14.349776</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6443,27 +6475,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
+          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6471,34 +6499,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6528,7 +6552,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786115129</t>
+          <t>1786122007</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6538,7 +6562,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13.559322</t>
+          <t>13.62862</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6555,28 +6579,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
+          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.4563</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6602,7 +6626,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6632,7 +6656,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786115128</t>
+          <t>1786117951</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6642,7 +6666,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>9.852217</t>
+          <t>43.769863</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6659,62 +6683,54 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
+          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.6812</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6744,7 +6760,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786116835</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6754,7 +6770,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>85.387755</t>
+          <t>1.467861</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6771,28 +6787,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
+          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>177.44126</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -6803,27 +6819,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6848,17 +6864,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786115830</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>350.501254</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6875,27 +6891,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
+          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.36999</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6903,11 +6915,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6915,27 +6923,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6960,17 +6968,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786111515</t>
+          <t>1786115829</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1.698514</t>
+          <t>1.985493</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6987,27 +6995,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
+          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7015,11 +7019,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7027,27 +7027,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786105696</t>
+          <t>1786115827</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>16.985121</t>
+          <t>1.463754</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7099,12 +7099,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
+          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7114,22 +7114,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4.49993</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.9463</t>
+          <t>1.3687</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Over 0.5</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786104752</t>
+          <t>1786115129</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>4.75554</t>
+          <t>13.559322</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7211,39 +7211,31 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
+          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5.99989</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1.5075</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Over 0.5</t>
-        </is>
-      </c>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7251,7 +7243,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7261,12 +7253,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7296,7 +7288,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786104743</t>
+          <t>1786115128</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7306,7 +7298,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>6.34909</t>
+          <t>9.852217</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7323,31 +7315,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7355,27 +7355,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7400,17 +7400,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786102413</t>
+          <t>1786115115</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>3.706122</t>
+          <t>85.387755</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7427,28 +7427,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>177.44126</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.2212</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7459,27 +7459,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7504,17 +7504,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786102412</t>
+          <t>1786115115</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>4.519774</t>
+          <t>350.501254</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7531,15 +7531,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>1</t>
@@ -7547,15 +7551,19 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7563,27 +7571,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7608,17 +7616,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786102410</t>
+          <t>1786111515</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2.416918</t>
+          <t>1.698514</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7635,31 +7643,39 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7682,7 +7698,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7712,7 +7728,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786102409</t>
+          <t>1786105696</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7722,7 +7738,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>5.128205</t>
+          <t>16.985121</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7739,12 +7755,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7754,22 +7770,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>4.49993</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.9463</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Over 0.5</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7779,7 +7795,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7789,12 +7805,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7824,7 +7840,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786096483</t>
+          <t>1786104752</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7834,7 +7850,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>151.554007</t>
+          <t>4.75554</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7851,12 +7867,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7866,22 +7882,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.99989</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.945</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Over 0.5</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7891,7 +7907,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Cambuur vs Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7901,12 +7917,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Excelsior Rotterdam</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7936,7 +7952,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786095316</t>
+          <t>1786104743</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7946,7 +7962,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>15.69338</t>
+          <t>6.34909</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7963,39 +7979,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -8003,27 +8011,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8048,17 +8056,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786086947</t>
+          <t>1786102413</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>503.272727</t>
+          <t>3.706122</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8075,39 +8083,31 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20.39624</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.2212</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -8115,27 +8115,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8160,17 +8160,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786082661</t>
+          <t>1786102412</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>54.389973</t>
+          <t>4.519774</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8187,28 +8187,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786102410</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>2.416918</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8291,28 +8291,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -8323,27 +8323,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8368,17 +8368,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786102409</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>5.128205</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8395,110 +8395,766 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>54.37</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1786096483</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>151.554007</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1786095316</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>15.69338</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1786086947</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>503.272727</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>20.39624</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.375</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1786082661</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>54.389973</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>14.19</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.5675</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1786076493</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>25.004405</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="V81" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Eredivisie/trades.xlsx
+++ b/data/sxbet/ligas/Eredivisie/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V81"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x690d059036b093e4b5b7c5348dcaf6e9c0038ffbd846a8822dfacb478490df81</t>
+          <t>0x8a8ed9adc1d4de3db5b94d80979b4d754a0d852489f65f9ebdff37a6445f6a90</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22.594</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6875</t>
+          <t>1.4663</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Go Ahead Eagles -1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x4882e1214422a29af689a209790d0484e91067d78c514ab50b9376875ef6c6da</t>
+          <t>0x0b4b5ebf9dca0a3c856e56dab394df00f40a416c0fccd6daeb0efd532e172815</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786172307</t>
+          <t>1786179522</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>32.864</t>
+          <t>14.906166</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x515f932c5d84342ff2016d68164d65c1b5e6c186e6404727ea74c0d2b65ce561</t>
+          <t>0x3e430c509937fe8d2b70a3d095bddd7d22d8f2a08c57223a174e63cdf0777725</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.67862</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AZ Alkmaar -2</t>
+          <t>NEC Nijmegen -2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xf88c6c4c9ed7484ff9bb259e779c42b8d62be41b33e50dbe39ff05ae3c3ced3d</t>
+          <t>0x1ad454c96c47b60c3469ca957e70ba1e03d07a5415f5e1d36eb27c71b1b71929</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786172307</t>
+          <t>1786178832</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>14.678024</t>
+          <t>42.526316</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x56584057b73ca4fdc229b61705b847a20afe82ac4a0c60c32239241b70855884</t>
+          <t>0xdf4b854c60a0d284680b173add96353100589a7cdc8c190f792332ab88e503d3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,22 +770,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.8313</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>NEC Nijmegen -2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
+          <t>0x1ad454c96c47b60c3469ca957e70ba1e03d07a5415f5e1d36eb27c71b1b71929</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786171005</t>
+          <t>1786177823</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>6.015002</t>
+          <t>46.140351</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x4988973efa2319ec17ed8f106880149d2870b9a4d2d1289bda5ef17eb6394876</t>
+          <t>0xfa4ef358eac452249f73e7fc61661edacb6f80ea2de8ebe4cbfbf18647d9e6eb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -875,23 +875,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.83583</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -914,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786170645</t>
+          <t>1786175564</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>18.265857</t>
+          <t>16.408759</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x1c5485873f863e5524d43f85a405dd076d4f362bfdb51537d55265f9b03bdfc3</t>
+          <t>0x3a748feb65ac248a85fcc0c30fd2effde4a871546382f53d8bcd05170e1c660d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -982,17 +990,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>11.07996</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2588</t>
+          <t>1.9287</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1018,7 +1026,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
+          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786170645</t>
+          <t>1786175542</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>19.439614</t>
+          <t>11.92997</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x8313f084f33c053a91835e9b9fa41d85e94dc7e2791909d44626fbdaafcc978c</t>
+          <t>0xb7878fc784f4da7ecef491e90e51d1b9cc39c46e6fb1eb088eb6de8952f3ab17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1090,22 +1098,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>54.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3088</t>
+          <t>1.1838</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AZ Alkmaar -2</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1115,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xf88c6c4c9ed7484ff9bb259e779c42b8d62be41b33e50dbe39ff05ae3c3ced3d</t>
+          <t>0xa9150d2c3375a454ebfef8c89c2b6e2fd82c39d2daa2de1cc42b81bf16bda763</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786165678</t>
+          <t>1786175541</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>17.619433</t>
+          <t>295.836735</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,39 +1195,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xe8ac9d951a75bfb5f85a9df2129b2402e3d7896e9994d96820f9c2abd9dfd94c</t>
+          <t>0xbfeee6360b04c1c72bacb54d7a04635e704d993e319d7ab8898aec38b9e83fbc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.59894</t>
+          <t>75.71998</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.855</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NEC Nijmegen -2</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x1ad454c96c47b60c3469ca957e70ba1e03d07a5415f5e1d36eb27c71b1b71929</t>
+          <t>0x656b05c8c9e0a63d26fa6dcc4ddf398d649bc013ac423819523cf94211567658</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786162832</t>
+          <t>1786175536</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>29.148949</t>
+          <t>88.56138</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xc2ff6b7ef5c4d6b1ae7fb27264146c018690220314bfbd5d9f754aed33050ad1</t>
+          <t>0x1c3c2b6bb8eb0767e968470d82bd9fe8dc04218d6af032ea0f5096f136bd4147</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1307,15 +1307,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.1787</t>
+          <t>1.1838</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1323,7 +1327,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1331,27 +1339,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
+          <t>0xa9150d2c3375a454ebfef8c89c2b6e2fd82c39d2daa2de1cc42b81bf16bda763</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1384,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786161973</t>
+          <t>1786175536</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>9.846154</t>
+          <t>30.639456</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,7 +1411,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x75f10c8c3b07bcf97178db485e61f1e964f7925053c699f8e7ae25fdef0517ba</t>
+          <t>0xdc34b5cbdb871b90d95a611d33368dbf531f4457695e9e7a1bcddaef406b8014</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1411,19 +1419,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>504.57991</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.1125</t>
+          <t>1.9287</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1431,11 +1435,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x2fbec757a98798a9e344fdcfeba32267077a6f189c5785b7b423a7d4efc507cd</t>
+          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786161973</t>
+          <t>1786175534</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>35.288889</t>
+          <t>543.289271</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xe31905b26a7e1536bf125b184f1294f656fa4f22b6e9fd739a0a032c4d321ce0</t>
+          <t>0xa0f2350445e080bec5921b48325cbf48c015b8e9c9baedd0a1997a09b42dbafa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1526,12 +1526,12 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9.73576</t>
+          <t>381.43995</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.1787</t>
+          <t>1.865</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1547,27 +1547,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
+          <t>0xc6686ae5e5b9bd3b1439d03b5fec466bdd019c255f84fe7e283b756924977214</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786161913</t>
+          <t>1786175534</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>54.46579</t>
+          <t>440.97104</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,39 +1619,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xb3bc0ed4c483bee8be05ae8fc496bbe64b2b2dad9597773c67ca17df236c46c6</t>
+          <t>0x79dc7157d2f976773c55533f385c8e3b7028e5f286572f64fb64f99aeb159652</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>267.62</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.9287</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1674,7 +1666,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786158954</t>
+          <t>1786175534</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>10.094545</t>
+          <t>288.15074</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,31 +1723,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x73f8172d3365445d5d6481e5b681390927b19eba83d829e34347ddf969f4d3aa</t>
+          <t>0x1888c773080fb6e570decb71f551855b67ac6d9b070d1f52bee5a80cea86fdc2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0xAAC601FEf8F6FBd4D17d515dA528e648f468E0A1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>249.5175</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.0925</t>
+          <t>1.8075</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x70ad3839eaf0acb3b01efaf7fbad4dc4e6d59e9cba36c93a59ba571f812853a5</t>
+          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786158954</t>
+          <t>1786175534</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>14.486486</t>
+          <t>309.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,28 +1835,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x49223560553949c798e427bb609beb8d54b408bb92fac667c5e805a35d272dd8</t>
+          <t>0x0fb2f416fa1d35845b08bd5aed33ce2d913ba958a1f6810aa06c4a3c628873ec</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.1738</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x9a0bc510c3953793967123d2592a887e55b2c7b4d336100e6a3528497b495765</t>
+          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1912,17 +1912,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786158687</t>
+          <t>1786175534</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.687764</t>
+          <t>48.978417</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,31 +1939,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x52a28d048aabdc20f81aa23618c25399119d945b7c7afae212c263d469fce473</t>
+          <t>0x3a14b1d812c2078a83f1b62e639b577331f33a8cd2f8b9f81992ce98b717dcce</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0x29c4c7668B1f9E7B037b36080Ea8682510C66b0e</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.0637</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -1986,7 +1994,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2016,7 +2024,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786158626</t>
+          <t>1786175533</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2026,7 +2034,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2.439024</t>
+          <t>288.156863</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,12 +2051,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x654ee8bcaf6b781089890f7528b8d264645cbb382b68a3166b49f74e9e50d5fa</t>
+          <t>0x196d1e274cce29838f456d958933aeb2fa99e583ee2a08ec2d0c408dcb328747</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2058,22 +2066,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.1425</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2083,27 +2091,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x700c0930687f6c1dc816f7af554f65cf4b2844ee77830f992d4a731c0df2564f</t>
+          <t>0x656b05c8c9e0a63d26fa6dcc4ddf398d649bc013ac423819523cf94211567658</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2128,17 +2136,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786158491</t>
+          <t>1786175533</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.033592</t>
+          <t>332.210526</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,12 +2163,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x38b906d6e5d0de2738537770dc05e6338898a8b937e89cbc914ae6e75513308b</t>
+          <t>0x12ea97d7182d78ee29f6db677b3d0ee9460702a5934f2946f242b147e432147a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2170,22 +2178,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>12.61711</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4838</t>
+          <t>1.1425</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2195,27 +2203,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x2ea149fa9b38b9090f5b506ae3dca75e0788add16a579f9705e6feb502e84868</t>
+          <t>0x656b05c8c9e0a63d26fa6dcc4ddf398d649bc013ac423819523cf94211567658</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2240,17 +2248,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786158491</t>
+          <t>1786175532</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.033592</t>
+          <t>88.541123</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2267,31 +2275,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x598f4044b8d7101954a12cfb6a028285705b009e647d167cb12be8cc1aa8c433</t>
+          <t>0x8def866b69852d97109315caa1798d40702c349cfb67eb7067c57e7b015999c4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>8.66588</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -2.5</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2299,27 +2315,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs SC Telstar</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x9455b4a5e4ea76ab5db55d0b29615eeae7a6c51e3bc31b5c6b0ed2395a188551</t>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19403940</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2344,17 +2360,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786158381</t>
+          <t>1786174998</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.781719</t>
+          <t>19.04589</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,28 +2387,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x7eaedb8f4752259366867abf771d84c0d99e47010227fd51681abeb60b48411b</t>
+          <t>0x8d4fe086df9f1b218dd2fd033023960a450955253f42e643e10e39a2306813eb</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76.6299</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.1638</t>
+          <t>1.9387</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2403,27 +2419,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xc998a4ccb6265ea2336288383810c1b769d49949dbefbe46fcd473372116b82c</t>
+          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2448,17 +2464,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786146812</t>
+          <t>1786174997</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>6.10687</t>
+          <t>81.62972</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,28 +2491,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xc17004473d1c14453448f29404ac7988d663c0f1eac3d80503d006f04db8d7a6</t>
+          <t>0x5eb9663de77899fd78a882feaedbe4d85e61e831851b717a0f6db9d9252491ce</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3725</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2507,27 +2523,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AZ Alkmaar vs ADO Den Haag</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x836ea569e8bb4a65752149e8c476f1184a85ddb5570c5106624ba137f9a0a2d5</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19404234</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2552,17 +2568,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786146806</t>
+          <t>1786172965</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2.684564</t>
+          <t>11.252336</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,31 +2595,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x88de27964fdb5afcbdf9d01c80c57e6ae6197056927b86aeb5d5e9260acc2828</t>
+          <t>0x690d059036b093e4b5b7c5348dcaf6e9c0038ffbd846a8822dfacb478490df81</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22.594</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.0775</t>
+          <t>1.6875</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2611,27 +2635,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xca6f32a50927cbde2cb395d95e723ecf21a4b1811b744369dad7d460f821dd6d</t>
+          <t>0x4882e1214422a29af689a209790d0484e91067d78c514ab50b9376875ef6c6da</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2656,17 +2680,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786146805</t>
+          <t>1786172307</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>12.903226</t>
+          <t>32.864</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,31 +2707,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x7c22fadfd0e1f902b93e750db5984c247214d30b4fe99214ef93a9e2ad497877</t>
+          <t>0x515f932c5d84342ff2016d68164d65c1b5e6c186e6404727ea74c0d2b65ce561</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.67862</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.1625</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar -2</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2715,27 +2747,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PEC Zwolle vs Ajax Amsterdam</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Ajax Amsterdam</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xdd44346ee5e92ddeb574c7b372f2f6e8cfcd74de2a5309e9003a1550bcc12ab0</t>
+          <t>0xf88c6c4c9ed7484ff9bb259e779c42b8d62be41b33e50dbe39ff05ae3c3ced3d</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19403941</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2760,17 +2792,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786146805</t>
+          <t>1786172307</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>6.153846</t>
+          <t>14.678024</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,12 +2819,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xb38a3cc2cf9c03f99487ec03657f937b47155f02bc75d79ffc33db76f98a69a6</t>
+          <t>0x56584057b73ca4fdc229b61705b847a20afe82ac4a0c60c32239241b70855884</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2802,22 +2834,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11.52135</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.8313</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -3</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2842,7 +2874,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2872,7 +2904,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786142904</t>
+          <t>1786171005</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2882,7 +2914,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>34.011365</t>
+          <t>6.015002</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,7 +2931,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x7a20466d35539c024b1d077354a8e89cf90472d7db1127f1ec7682095c931015</t>
+          <t>0x4988973efa2319ec17ed8f106880149d2870b9a4d2d1289bda5ef17eb6394876</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2907,31 +2939,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9.70945</t>
+          <t>3.83583</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -2954,7 +2978,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2984,7 +3008,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786142904</t>
+          <t>1786170645</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2994,7 +3018,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>21.339451</t>
+          <t>18.265857</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3011,39 +3035,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x3e2fa39473c09803be951522f0cce2a88e71007867e0d6a0ae033e851124bc38</t>
+          <t>0x1c5485873f863e5524d43f85a405dd076d4f362bfdb51537d55265f9b03bdfc3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>367.52999</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.2588</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3051,27 +3067,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3096,17 +3112,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786142696</t>
+          <t>1786170645</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>624.25476</t>
+          <t>19.439614</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3123,31 +3139,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xd9c75ae7cbf7ebba9529c5699532d10d62802be6aac9ffc45052aa92cc35d72d</t>
+          <t>0x8313f084f33c053a91835e9b9fa41d85e94dc7e2791909d44626fbdaafcc978c</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3362</t>
+          <t>1.3088</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar -2</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3170,7 +3194,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x4882e1214422a29af689a209790d0484e91067d78c514ab50b9376875ef6c6da</t>
+          <t>0xf88c6c4c9ed7484ff9bb259e779c42b8d62be41b33e50dbe39ff05ae3c3ced3d</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3200,7 +3224,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786142027</t>
+          <t>1786165678</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3210,7 +3234,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>50.64684</t>
+          <t>17.619433</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3227,7 +3251,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x417760c1d35fd131f695db2c7f2e8400a5d3d5d5903b79ac1ca222a5a30d0134</t>
+          <t>0xe8ac9d951a75bfb5f85a9df2129b2402e3d7896e9994d96820f9c2abd9dfd94c</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3242,12 +3266,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>8.59894</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5663</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3257,7 +3281,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -2</t>
+          <t>NEC Nijmegen -2</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3267,27 +3291,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xd9978e221ac5eb1139faeeefdedfd12ffe6f1986a602f6669e76abce9bb9067d</t>
+          <t>0x1ad454c96c47b60c3469ca957e70ba1e03d07a5415f5e1d36eb27c71b1b71929</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3312,17 +3336,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786140016</t>
+          <t>1786162832</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2.101545</t>
+          <t>29.148949</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3339,7 +3363,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x16fd77e28d16ec069fe859b1ad63a1ce956b06b6136d6ac68ccdb02be6b3c94c</t>
+          <t>0xc2ff6b7ef5c4d6b1ae7fb27264146c018690220314bfbd5d9f754aed33050ad1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3350,12 +3374,12 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.8475</t>
+          <t>1.1787</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3371,27 +3395,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs SC Telstar</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x656b05c8c9e0a63d26fa6dcc4ddf398d649bc013ac423819523cf94211567658</t>
+          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19403940</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3416,17 +3440,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786136525</t>
+          <t>1786161973</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>11.79941</t>
+          <t>9.846154</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,7 +3467,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xd3c8bb8d02330d8124e995d21959103edcd0baaa6289b159970a2225912e418d</t>
+          <t>0x75f10c8c3b07bcf97178db485e61f1e964f7925053c699f8e7ae25fdef0517ba</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3451,23 +3475,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.1125</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3490,7 +3522,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
+          <t>0x2fbec757a98798a9e344fdcfeba32267077a6f189c5785b7b423a7d4efc507cd</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3520,7 +3552,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786135338</t>
+          <t>1786161973</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3530,7 +3562,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>4.792453</t>
+          <t>35.288889</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3547,7 +3579,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xbdbdd9823b5c0238c109c0b23805ef0ff9a61aa34409f875e76398a0a7d6a460</t>
+          <t>0xe31905b26a7e1536bf125b184f1294f656fa4f22b6e9fd739a0a032c4d321ce0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3558,17 +3590,17 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>9.73576</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.1787</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3594,7 +3626,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
+          <t>0xea73d36b737bbb8283ce65587dc85f7842e6e2afc8a231e10311590ace9c256d</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3624,7 +3656,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786135338</t>
+          <t>1786161913</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3634,7 +3666,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>181.283019</t>
+          <t>54.46579</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3651,7 +3683,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x6e5e8a0fc2f92f97555f424e1454c8c7768aee012cd36da5c6482cae7684c76a</t>
+          <t>0xb3bc0ed4c483bee8be05ae8fc496bbe64b2b2dad9597773c67ca17df236c46c6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3666,12 +3698,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3736,7 +3768,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786135337</t>
+          <t>1786158954</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3746,7 +3778,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>7.577358</t>
+          <t>10.094545</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3763,7 +3795,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xe9b4cf790ad6491c958a9df98bf381066cbab97000c72aaa03df184df175418c</t>
+          <t>0x73f8172d3365445d5d6481e5b681390927b19eba83d829e34347ddf969f4d3aa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3771,31 +3803,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.36113</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.0925</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3818,7 +3842,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0x70ad3839eaf0acb3b01efaf7fbad4dc4e6d59e9cba36c93a59ba571f812853a5</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3848,7 +3872,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786135296</t>
+          <t>1786158954</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3858,7 +3882,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>25.241147</t>
+          <t>14.486486</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3875,39 +3899,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xadbd273938f30f3bb961943289c77aa5d38f5773b41a5f47fdaa69aaae6f92c6</t>
+          <t>0x49223560553949c798e427bb609beb8d54b408bb92fac667c5e805a35d272dd8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.6513</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>NEC Nijmegen</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -3915,27 +3931,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs SC Telstar</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SC Telstar</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x8a99a50823ade222f81f1405d35b66126a5baec6c8557587d907d6fc42ee8959</t>
+          <t>0x9a0bc510c3953793967123d2592a887e55b2c7b4d336100e6a3528497b495765</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19403940</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3960,17 +3976,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786133357</t>
+          <t>1786158687</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786199400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>7.677543</t>
+          <t>1.687764</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3987,39 +4003,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x1fcc69e05756a9495c54cf92ec95cc3fa98841963ff82dbc95bde1118d0e88d6</t>
+          <t>0x52a28d048aabdc20f81aa23618c25399119d945b7c7afae212c263d469fce473</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>13.75169</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>PSV Eindhoven -3</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4042,7 +4050,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4072,7 +4080,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786132692</t>
+          <t>1786158626</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4082,7 +4090,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>41.514536</t>
+          <t>2.439024</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4099,31 +4107,39 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x633e302e1f4a45e6cae190310048fc5640fdefddf9379c3100fb1c66a99ed226</t>
+          <t>0x654ee8bcaf6b781089890f7528b8d264645cbb382b68a3166b49f74e9e50d5fa</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>855.42</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4131,27 +4147,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x700c0930687f6c1dc816f7af554f65cf4b2844ee77830f992d4a731c0df2564f</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4176,17 +4192,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786129763</t>
+          <t>1786158491</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1555.309091</t>
+          <t>1.033592</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4203,31 +4219,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x0630cb5bb6cb2cff5cff3d307163d367059153070ce4cc710f35aa8d5c0c6825</t>
+          <t>0x38b906d6e5d0de2738537770dc05e6338898a8b937e89cbc914ae6e75513308b</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4838</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -4235,27 +4259,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x2ea149fa9b38b9090f5b506ae3dca75e0788add16a579f9705e6feb502e84868</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4280,17 +4304,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786129750</t>
+          <t>1786158491</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>132.545455</t>
+          <t>1.033592</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4307,28 +4331,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x7935024ab7987fd550aa17e789e9bdc95e2fbd51b52763713f00cf3fdfce8bdd</t>
+          <t>0x598f4044b8d7101954a12cfb6a028285705b009e647d167cb12be8cc1aa8c433</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>14.33</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4339,27 +4363,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x9455b4a5e4ea76ab5db55d0b29615eeae7a6c51e3bc31b5c6b0ed2395a188551</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4384,17 +4408,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786129738</t>
+          <t>1786158381</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>26.054545</t>
+          <t>1.781719</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4411,28 +4435,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x2b5a8f7ff44e3e83441016e9d07c7203d32fcbd029be82f693028e41ea14167e</t>
+          <t>0x7eaedb8f4752259366867abf771d84c0d99e47010227fd51681abeb60b48411b</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6.20999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.1638</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -4443,27 +4467,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc998a4ccb6265ea2336288383810c1b769d49949dbefbe46fcd473372116b82c</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4488,17 +4512,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786129725</t>
+          <t>1786146812</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>11.290891</t>
+          <t>6.10687</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4515,28 +4539,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x9be5cfaca91d026b377dc51c41481c7420f402caa117cd1a71bf175f81b8ba3f</t>
+          <t>0xc17004473d1c14453448f29404ac7988d663c0f1eac3d80503d006f04db8d7a6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4547,27 +4571,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x836ea569e8bb4a65752149e8c476f1184a85ddb5570c5106624ba137f9a0a2d5</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4592,17 +4616,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786129713</t>
+          <t>1786146806</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>31.436364</t>
+          <t>2.684564</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4619,28 +4643,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xffdb31c98c0c9e42bd2a3a4ac8c08c4dddf1bac9229455355ddf0f61eda11f5f</t>
+          <t>0x88de27964fdb5afcbdf9d01c80c57e6ae6197056927b86aeb5d5e9260acc2828</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>52.93</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.0775</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4651,27 +4675,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xca6f32a50927cbde2cb395d95e723ecf21a4b1811b744369dad7d460f821dd6d</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4696,17 +4720,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786129699</t>
+          <t>1786146805</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>96.236364</t>
+          <t>12.903226</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4723,28 +4747,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x171c10e2c280f22ecd4a761a066bbcf7603ce72eb3464dbacf9b961ad202fb59</t>
+          <t>0x7c22fadfd0e1f902b93e750db5984c247214d30b4fe99214ef93a9e2ad497877</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>215.36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.1625</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4755,27 +4779,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PEC Zwolle vs Ajax Amsterdam</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Ajax Amsterdam</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xdd44346ee5e92ddeb574c7b372f2f6e8cfcd74de2a5309e9003a1550bcc12ab0</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403941</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4800,17 +4824,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786129686</t>
+          <t>1786146805</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>391.563636</t>
+          <t>6.153846</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4827,7 +4851,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x5ea684350a1a0b65d0f38be341db1516c1df4fe66d544944688193d0c3e3f0de</t>
+          <t>0xb38a3cc2cf9c03f99487ec03657f937b47155f02bc75d79ffc33db76f98a69a6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4842,22 +4866,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>495.02</t>
+          <t>11.52135</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>PSV Eindhoven -3</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4867,27 +4891,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4912,17 +4936,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786129356</t>
+          <t>1786142904</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>995.015075</t>
+          <t>34.011365</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4939,7 +4963,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x1a61ba580443c208fcf8a35afa56d0df4aaad017c49874a664c65a6551ec7d84</t>
+          <t>0x7a20466d35539c024b1d077354a8e89cf90472d7db1127f1ec7682095c931015</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4954,22 +4978,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>495.02</t>
+          <t>9.70945</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>PSV Eindhoven -2.5</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4979,27 +5003,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5024,17 +5048,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786129323</t>
+          <t>1786142904</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>995.015075</t>
+          <t>21.339451</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,12 +5075,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xbc4a52ef8f6d90db800339bd0fdc45e1e4887cc29721741fa364564427cebc93</t>
+          <t>0x3e2fa39473c09803be951522f0cce2a88e71007867e0d6a0ae033e851124bc38</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5066,22 +5090,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>367.52999</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5091,27 +5115,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Willem II Tilburg</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403947</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5136,17 +5160,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786129297</t>
+          <t>1786142696</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786207500</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>97.507538</t>
+          <t>624.25476</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5163,39 +5187,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x009e27d36e3bfb01593b611eb8138842f7baf97d375a4302c10337f4fa65da7a</t>
+          <t>0xd9c75ae7cbf7ebba9529c5699532d10d62802be6aac9ffc45052aa92cc35d72d</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.3362</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5203,27 +5219,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>AZ Alkmaar vs ADO Den Haag</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
+          <t>0x4882e1214422a29af689a209790d0484e91067d78c514ab50b9376875ef6c6da</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19404234</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5248,17 +5264,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786128259</t>
+          <t>1786142027</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>152.897196</t>
+          <t>50.64684</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5275,7 +5291,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x987370b50d0502b7fd566ef6bb2bf38112c25bf81110ad0b1926b02ffd8ccd9d</t>
+          <t>0x417760c1d35fd131f695db2c7f2e8400a5d3d5d5903b79ac1ca222a5a30d0134</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5290,22 +5306,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.5663</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PSV Eindhoven -3</t>
+          <t>PSV Eindhoven -2</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5330,7 +5346,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
+          <t>0xd9978e221ac5eb1139faeeefdedfd12ffe6f1986a602f6669e76abce9bb9067d</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5360,7 +5376,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786127657</t>
+          <t>1786140016</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5370,7 +5386,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>5.94717</t>
+          <t>2.101545</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5387,7 +5403,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x38207556aceeaaa6ba9394fe5b398b808e1d67e0bba9c3b0fa61a88d5c5aebb7</t>
+          <t>0x16fd77e28d16ec069fe859b1ad63a1ce956b06b6136d6ac68ccdb02be6b3c94c</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5395,19 +5411,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>21.40562</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.0737</t>
+          <t>1.8475</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5415,11 +5427,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Fortuna Sittard</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -5427,27 +5435,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
+          <t>0x656b05c8c9e0a63d26fa6dcc4ddf398d649bc013ac423819523cf94211567658</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5472,17 +5480,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786126212</t>
+          <t>1786136525</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>290.245695</t>
+          <t>11.79941</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5499,7 +5507,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x83a78ff6339d485633ea010240dad1c0ad7f4a30a2628cd7eb01ab0370275ddc</t>
+          <t>0xd3c8bb8d02330d8124e995d21959103edcd0baaa6289b159970a2225912e418d</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5510,17 +5518,17 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4.76023</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -5531,27 +5539,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5576,17 +5584,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786125622</t>
+          <t>1786135338</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>10.292389</t>
+          <t>4.792453</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5603,28 +5611,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x5630ba52ae08208c16f996b3fc5f0ab29f63363f75b764a890d5196f1a24e9b9</t>
+          <t>0xbdbdd9823b5c0238c109c0b23805ef0ff9a61aa34409f875e76398a0a7d6a460</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x6e70489F443F69f1a091af8509f0b99338460D39</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>249.99999</t>
+          <t>48.04</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5635,27 +5643,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xa6b60b40c7557b2592f67483af15406daf50c611685a083940ada784e2120a64</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5680,17 +5688,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786125585</t>
+          <t>1786135338</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>469.483549</t>
+          <t>181.283019</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5707,59 +5715,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x272659eb9c2a40b218a61bdb98731190ae92104b09c8c08096e7cacce4e2dc79</t>
+          <t>0x6e5e8a0fc2f92f97555f424e1454c8c7768aee012cd36da5c6482cae7684c76a</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5784,17 +5800,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786125525</t>
+          <t>1786135337</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>9.389671</t>
+          <t>7.577358</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5811,59 +5827,67 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xc8538d15c53a4c377da962db1d0193aab217862d8ad9ac90a3999b587e2a1c53</t>
+          <t>0xe9b4cf790ad6491c958a9df98bf381066cbab97000c72aaa03df184df175418c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>76.29599</t>
+          <t>8.36113</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.5312</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven -3</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5888,17 +5912,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786125507</t>
+          <t>1786135296</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>143.615981</t>
+          <t>25.241147</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5915,12 +5939,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xcb1bccb079df818106a903bda81def1d78bea048113133314cb9b5de80505b9a</t>
+          <t>0xadbd273938f30f3bb961943289c77aa5d38f5773b41a5f47fdaa69aaae6f92c6</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xBc04c6a7E9255Cb262632407a40Aa6344137555b</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5930,12 +5954,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4.14001</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.6513</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5945,7 +5969,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5955,27 +5979,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>SC Telstar</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x8a99a50823ade222f81f1405d35b66126a5baec6c8557587d907d6fc42ee8959</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403940</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6000,17 +6024,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786124259</t>
+          <t>1786133357</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786199400</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>10.894763</t>
+          <t>7.677543</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6027,7 +6051,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x7b5620344652130ca3f87e52b00289e9ee38aab6c426c0e9cd693b417361526c</t>
+          <t>0x1fcc69e05756a9495c54cf92ec95cc3fa98841963ff82dbc95bde1118d0e88d6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6042,22 +6066,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13.75169</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven -3</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6067,27 +6091,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6112,17 +6136,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786124259</t>
+          <t>1786132692</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>157.894737</t>
+          <t>41.514536</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6139,7 +6163,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xdc6c27f0359af82e276a61c449bef19ee4c2778a601eecfac8b0ae278c4fed31</t>
+          <t>0x633e302e1f4a45e6cae190310048fc5640fdefddf9379c3100fb1c66a99ed226</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6147,54 +6171,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>855.42</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.3787</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6224,7 +6240,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786124228</t>
+          <t>1786129763</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6234,7 +6250,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>168.844884</t>
+          <t>1555.309091</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6251,7 +6267,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xb740a9883984f2d057b5bd144c80df89d3be4972b6802619769be156582f7530</t>
+          <t>0x0630cb5bb6cb2cff5cff3d307163d367059153070ce4cc710f35aa8d5c0c6825</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6259,54 +6275,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>56.08</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.3725</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6336,7 +6344,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786123222</t>
+          <t>1786129750</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6346,7 +6354,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>150.550336</t>
+          <t>132.545455</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6363,39 +6371,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x1eb675eb4dddff6e46c7fe87ea19a03c7d5274c16759609d8d9cad3c46312d55</t>
+          <t>0x7935024ab7987fd550aa17e789e9bdc95e2fbd51b52763713f00cf3fdfce8bdd</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786123213</t>
+          <t>1786129738</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>14.349776</t>
+          <t>26.054545</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6475,28 +6475,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
+          <t>0x2b5a8f7ff44e3e83441016e9d07c7203d32fcbd029be82f693028e41ea14167e</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6.20999</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786122007</t>
+          <t>1786129725</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13.62862</t>
+          <t>11.290891</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6579,28 +6579,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
+          <t>0x9be5cfaca91d026b377dc51c41481c7420f402caa117cd1a71bf175f81b8ba3f</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.4563</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786117951</t>
+          <t>1786129713</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>43.769863</t>
+          <t>31.436364</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6683,28 +6683,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
+          <t>0xffdb31c98c0c9e42bd2a3a4ac8c08c4dddf1bac9229455355ddf0f61eda11f5f</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.99998</t>
+          <t>52.93</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.6812</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786116835</t>
+          <t>1786129699</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1.467861</t>
+          <t>96.236364</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6787,28 +6787,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
+          <t>0x171c10e2c280f22ecd4a761a066bbcf7603ce72eb3464dbacf9b961ad202fb59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>215.36</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -6819,27 +6819,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6864,17 +6864,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786115830</t>
+          <t>1786129686</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>391.563636</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6891,31 +6891,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
+          <t>0x5ea684350a1a0b65d0f38be341db1516c1df4fe66d544944688193d0c3e3f0de</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.36999</t>
+          <t>495.02</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -6923,27 +6931,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6968,17 +6976,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786115829</t>
+          <t>1786129356</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1.985493</t>
+          <t>995.015075</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6995,31 +7003,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
+          <t>0x1a61ba580443c208fcf8a35afa56d0df4aaad017c49874a664c65a6551ec7d84</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>495.02</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7027,27 +7043,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>FC Groningen vs FC Utrecht</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19403944</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7072,17 +7088,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786115827</t>
+          <t>1786129323</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786278600</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1.463754</t>
+          <t>995.015075</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7099,12 +7115,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
+          <t>0xbc4a52ef8f6d90db800339bd0fdc45e1e4887cc29721741fa364564427cebc93</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7114,47 +7130,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.3687</t>
+          <t>1.4975</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7184,7 +7200,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786115129</t>
+          <t>1786129297</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7194,7 +7210,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>13.559322</t>
+          <t>97.507538</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7211,36 +7227,44 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
+          <t>0x009e27d36e3bfb01593b611eb8138842f7baf97d375a4302c10337f4fa65da7a</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>Cambuur vs Excelsior Rotterdam FC</t>
@@ -7258,7 +7282,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0xb17c3764ecbc4658a26959356523b3f4e8d33367229f845391540d30046fc66f</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7288,7 +7312,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786115128</t>
+          <t>1786128259</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7298,7 +7322,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>9.852217</t>
+          <t>152.897196</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7315,12 +7339,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
+          <t>0x987370b50d0502b7fd566ef6bb2bf38112c25bf81110ad0b1926b02ffd8ccd9d</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7330,22 +7354,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven -3</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7355,27 +7379,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xc0728bb541cc25968730e404ea7ba8f4ea1f480376e08b6abc943ea8ad3b2ca9</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7400,17 +7424,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786127657</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>85.387755</t>
+          <t>5.94717</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7427,59 +7451,67 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
+          <t>0x38207556aceeaaa6ba9394fe5b398b808e1d67e0bba9c3b0fa61a88d5c5aebb7</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>177.44126</t>
+          <t>21.40562</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.0737</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+          <t>0x64e4fcefd58dcda365098535597b1cf41bef3afc8e914d74c09e4aa3b69534e1</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403946</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7504,17 +7536,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786115115</t>
+          <t>1786126212</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786212000</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>350.501254</t>
+          <t>290.245695</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7531,39 +7563,31 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
+          <t>0x83a78ff6339d485633ea010240dad1c0ad7f4a30a2628cd7eb01ab0370275ddc</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.76023</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7571,27 +7595,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7616,17 +7640,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786111515</t>
+          <t>1786125622</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1.698514</t>
+          <t>10.292389</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7643,39 +7667,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
+          <t>0x5630ba52ae08208c16f996b3fc5f0ab29f63363f75b764a890d5196f1a24e9b9</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x6e70489F443F69f1a091af8509f0b99338460D39</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>249.99999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7683,27 +7699,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7728,17 +7744,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786105696</t>
+          <t>1786125585</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>16.985121</t>
+          <t>469.483549</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7755,39 +7771,31 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
+          <t>0x272659eb9c2a40b218a61bdb98731190ae92104b09c8c08096e7cacce4e2dc79</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.49993</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.9463</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Over 0.5</t>
-        </is>
-      </c>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7795,7 +7803,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7805,12 +7813,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7840,7 +7848,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786104752</t>
+          <t>1786125525</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7850,7 +7858,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>4.75554</t>
+          <t>9.389671</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7867,39 +7875,31 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
+          <t>0xc8538d15c53a4c377da962db1d0193aab217862d8ad9ac90a3999b587e2a1c53</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5.99989</t>
+          <t>76.29599</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.945</t>
+          <t>1.5312</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Over 0.5</t>
-        </is>
-      </c>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786104743</t>
+          <t>1786125507</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>6.34909</t>
+          <t>143.615981</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7979,31 +7979,39 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+          <t>0xcb1bccb079df818106a903bda81def1d78bea048113133314cb9b5de80505b9a</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>4.14001</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -8011,27 +8019,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8056,17 +8064,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786102413</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>3.706122</t>
+          <t>10.894763</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8083,31 +8091,39 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+          <t>0x7b5620344652130ca3f87e52b00289e9ee38aab6c426c0e9cd693b417361526c</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.2212</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -8115,27 +8131,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8160,17 +8176,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786102412</t>
+          <t>1786124259</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>4.519774</t>
+          <t>157.894737</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8187,31 +8203,39 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+          <t>0xdc6c27f0359af82e276a61c449bef19ee4c2778a601eecfac8b0ae278c4fed31</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.3787</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -8219,27 +8243,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8264,17 +8288,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786102410</t>
+          <t>1786124228</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>2.416918</t>
+          <t>168.844884</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8291,31 +8315,39 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+          <t>0xb740a9883984f2d057b5bd144c80df89d3be4972b6802619769be156582f7530</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>56.08</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.3725</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -8323,27 +8355,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19403947</t>
+          <t>L19403942</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8368,17 +8400,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786102409</t>
+          <t>1786123222</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1786207500</t>
+          <t>1786125600</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>5.128205</t>
+          <t>150.550336</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8395,12 +8427,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+          <t>0x1eb675eb4dddff6e46c7fe87ea19a03c7d5274c16759609d8d9cad3c46312d55</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8410,12 +8442,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8425,32 +8457,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8480,7 +8512,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786096483</t>
+          <t>1786123213</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8490,7 +8522,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>151.554007</t>
+          <t>14.349776</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8507,27 +8539,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+          <t>0x7508f4945131f4e01d80e88b9e39dc04a40426c9cb85c4bf01cdb9c26b334506</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x5b6BBebB45EA5796CF7b9459be5785fbE7Ffaf90</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.3588</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8535,34 +8563,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0xb8be8ed08f9d9854060b52b49f1811c191bd0c1616e1b093b28a4e78ee57154b</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8592,7 +8616,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786095316</t>
+          <t>1786122007</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8602,7 +8626,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>15.69338</t>
+          <t>13.62862</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8619,39 +8643,31 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+          <t>0xfaf4beff3b7f9403b40b5b13cdf01850a5090f98754d18ca5f83f066da413540</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.4563</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>Eredivisie</t>
@@ -8674,7 +8690,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0x16fabaade5687754bb46d8491b53388dc9815cef412e67a28d99cace1f9401a7</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8704,7 +8720,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786086947</t>
+          <t>1786117951</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8714,7 +8730,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>503.272727</t>
+          <t>43.769863</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8731,62 +8747,54 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+          <t>0x5ded18ee9cf6d0038c25bfcf4cdaa513fe3f5574ccbf784436b2d6d1a93f94bb</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xC3dd311005D417d573090717c8981A244b010aDc</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20.39624</t>
+          <t>0.99998</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.375</t>
+          <t>1.6812</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam FC</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Cambuur</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Excelsior Rotterdam FC</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8816,7 +8824,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786082661</t>
+          <t>1786116835</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8826,7 +8834,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>54.389973</t>
+          <t>1.467861</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8843,7 +8851,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+          <t>0x4e752655ff6e177e1cb3bc0a594bc3d4797ae02f5942f50c529961f6934acd10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8854,17 +8862,17 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.5675</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -8875,27 +8883,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>PSV Eindhoven vs Fortuna Sittard</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19403946</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8920,17 +8928,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786076493</t>
+          <t>1786115830</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1786212000</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>25.004405</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8947,28 +8955,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+          <t>0xeda1b6d90374f6dfb1eb5db7e196f22b05428f1c82d7c343bc33c73b67266d78</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>1.36999</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.6338</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -8979,27 +8987,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Cambuur vs Excelsior Rotterdam FC</t>
+          <t>FC Groningen vs FC Utrecht</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Excelsior Rotterdam FC</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19403942</t>
+          <t>L19403944</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -9024,17 +9032,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786044588</t>
+          <t>1786115829</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1786125600</t>
+          <t>1786278600</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>66.571992</t>
+          <t>1.985493</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9051,110 +9059,2166 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>0x5a3f9702291c1ba964abe33fedccffcf9d3ad9537235ab7b839f5865be46b8a5</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1.00999</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>FC Groningen vs FC Utrecht</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>FC Groningen</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>FC Utrecht</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0xade4255f0990d680e7f97af3f0657bc324f1ff60d7a5809184574fdacbbbb3be</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19403944</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1786115827</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1786278600</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1.463754</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0x766cd6df2eab89155d957f9e8c70e449311d87969614090438e8172ea68e472d</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.3687</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1786115129</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>13.559322</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0x1c3956d4fd671eb8f64e9c1dde1907d26d4ca3284611bf2166ba25878ada840d</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1786115128</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>9.852217</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0xd45d17af5b95ec1c1350bb1787486845b1e75220b35567f190918eb7f442b573</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>31.38</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.3675</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1786115115</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>85.387755</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0xc314db881b3e02a32691c317283fd9a8fdab70d92c17be01a655abfdbd237005</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>177.44126</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.5063</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0x9ab95655b7491fc8e615c8d50d6b5fe19a0750663b098d28624ff47a889afa65</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1786115115</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>350.501254</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0x30e80e0f179988de24d2dd1521c00c47b8a96c2e0b127f5b72b5656e3f3c392a</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0xFe080e9732dfD21D183C50e533A0B4b16021512a</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.5888</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19403947</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1786111515</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1786207500</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1.698514</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0x5814ac08c32ab173d1a31814cb3a6b884d7c9919e8f377ee4f05aeaa32cb47ee</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>9.99999</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.5888</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0x8aa5f120fe51985c65586c394c669657f5118efb952dee047f9dabfcbeb011d3</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19403947</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1786105696</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1786207500</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>16.985121</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0xf98e5cfa7926a69ff6e557c416734c337a5cb9347da000cf0a1b8afd308312c1</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>4.49993</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.9463</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1786104752</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>4.75554</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0x85052153f0e8ac58dbcbeb02f546bbc166e1c5e3e8753d3dee4219a55150e22d</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0xCf35f1782f282b1c6659882a3FAA48C637Ab693b</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>5.99989</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.945</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0x1decb278c23c8109eb9cf89c45fcff13cc3065960479465ded1dc8684e6e3f1f</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1786104743</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>6.34909</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0xc99b1deff403bd60532b3766c532f84759f6d39b1bdbf56a0da46442c81b8dbe</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.6125</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0xd10635672e9e5618b0fee4290a52fdad51735dc4dfbd7ede4bc2a4e63cc90c47</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1786102413</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>3.706122</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0x557b8c1f5c5c8b5fb903d079ecd882cabc34a595be512242ec8c9f410dc89cc8</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.2212</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0x655963edf32f16b3a45d6a00e88736f6309fec1474356ce20fc40bcb6fec13aa</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>1786102412</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>4.519774</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0xd876072232054549cb6720da6ed0929158b37dc7f9e1ed70e03cf4bb6785214e</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0x8e63f170dc54d5f8c63f531a5dcccded818e9d9e5f10a9596397c42875b381c7</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1786102410</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>2.416918</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0xfb67071ab7e9a27f540fd95f339b51a0fac006bd9950b6d733ec4be68c85bb16</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0xbFA1723b261cB748697a7FFc3236E1c7C04bfC5e</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.195</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles vs Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>0x850e00f49e80137284f56035827d7137ff8b0500f064e9bbebfb9172d34d807c</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>L19403947</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>1786102409</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>1786207500</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>5.128205</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0xe3ab30d6b781a9a79b98b5a3c156060adf02a4cb6dd79257d045954564c464f4</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>54.37</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1786096483</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>151.554007</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0xfcb42550a86c19b2c5cb5270b8fbf7ab1826b37014cd165720a9eba42002beba</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.3588</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>1786095316</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>15.69338</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0xd6c7c9abba838597a4e77b3e2783253562734141d39ee275990cdeca84ed5917</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0x8Aba6E6af9321Edf3b1b3b1CA92adEdb93D247C6</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>1786086947</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>503.272727</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0x9f01fbafa94a70a9cf6ab60945073f6a9cfd9c030489c2f7ad0e408d82e12640</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>20.39624</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.375</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0xaa0c126d35fe767a756910f2acec4006318f8fe1dab75625727393f8adb31b74</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1786082661</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>54.389973</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0x763d8974248de39c38179dce6fdf8aabf07c45a9532c44fd941f4ecaa4053020</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>14.19</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.5675</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>0x793b0538f962d70a57b2c5c4acd58d7dd39a82bb4331ea1b3fa94033d70c07e7</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>L19403946</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>1786076493</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>1786212000</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>25.004405</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0xbe3757de0d107fa27fec050f220d2720a303c2274c5053b041e64a8587c5429d</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>42.19</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.6338</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Cambuur vs Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Excelsior Rotterdam FC</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>0x5f73abff6c3a4dcbae7549384a24a6e32ed4fba83d1f8b6c07a54368215ec4b8</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>L19403942</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>1786044588</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>1786125600</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>66.571992</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>0x4ca810464ed1f6cc74ea5318f5d93dec93f4b441fa85a47c53e1f17f3dc3f2ff</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>35.25</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>1.195</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>NEC Nijmegen vs SC Telstar</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>NEC Nijmegen</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>SC Telstar</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>0x32e22d2bad4d17213f93e2773019169fc54af66f0156ef2678851d836d908f54</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>L19403940</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
         <is>
           <t>1786038454</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>1786199400</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>180.769231</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="U100" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr">
+      <c r="V100" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
